--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A72F609-405F-7741-9CB3-AC4C971CEB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F63D24-631E-1245-97A2-2A05D2850843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Übungsliste" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="253">
   <si>
     <t>Übung</t>
   </si>
@@ -165,9 +165,6 @@
     <t>■ LAT</t>
   </si>
   <si>
-    <t>Klimmzug, supiniert, schulterbreit</t>
-  </si>
-  <si>
     <t>Lat</t>
   </si>
   <si>
@@ -195,9 +192,6 @@
     <t>Bizeps</t>
   </si>
   <si>
-    <t>Kabel Latziehen, schulterbreit, supiniert</t>
-  </si>
-  <si>
     <t>KH Rudern, eng, neutral</t>
   </si>
   <si>
@@ -219,45 +213,15 @@
     <t>■ OBERER RÜCKEN</t>
   </si>
   <si>
-    <t>LH Rudern, weit, proniert</t>
-  </si>
-  <si>
     <t>Oberer Rücken</t>
   </si>
   <si>
     <t>Lat, Bizeps, Hintere Schulter</t>
   </si>
   <si>
-    <t>Multipresse Rudern, weit, proniert</t>
-  </si>
-  <si>
-    <t>PL Rudern, weit, proniert</t>
-  </si>
-  <si>
-    <t>Steck Rudern, weit, proniert</t>
-  </si>
-  <si>
-    <t>Kabel Rudern, weit, proniert</t>
-  </si>
-  <si>
-    <t>LH Rudern, schulterbreit, supiniert</t>
-  </si>
-  <si>
     <t>Lat, Bizeps</t>
   </si>
   <si>
-    <t>Multipresse Rudern, schulterbreit, supiniert</t>
-  </si>
-  <si>
-    <t>Steck Rudern, weit, supiniert</t>
-  </si>
-  <si>
-    <t>Kabel Rudern, weit, supiniert</t>
-  </si>
-  <si>
-    <t>LH T-Bar Rudern</t>
-  </si>
-  <si>
     <t>PL T-Bar Rudern</t>
   </si>
   <si>
@@ -297,9 +261,6 @@
     <t>LH Frontdrücken</t>
   </si>
   <si>
-    <t>Seitliche Schulter, Trizeps, Oberer Rücken</t>
-  </si>
-  <si>
     <t>Multipresse Frontdrücken</t>
   </si>
   <si>
@@ -393,12 +354,6 @@
     <t>■ HINTERE SCHULTER</t>
   </si>
   <si>
-    <t>KH Seitheben, vorgebeugt, proniert</t>
-  </si>
-  <si>
-    <t>Kabel Seitheben, vorgebeugt, proniert</t>
-  </si>
-  <si>
     <t>KH Reverse Flys</t>
   </si>
   <si>
@@ -420,9 +375,6 @@
     <t>Unterarme</t>
   </si>
   <si>
-    <t>KH Konzentrationscurls, supiniert</t>
-  </si>
-  <si>
     <t>KH Schrägbankcurls, Untergriff</t>
   </si>
   <si>
@@ -784,6 +736,54 @@
   </si>
   <si>
     <t>Klimmzug, Obergriff, weit</t>
+  </si>
+  <si>
+    <t>Klimmzug, Untergriff, schulterbreit</t>
+  </si>
+  <si>
+    <t>Kabel Latziehen, schulterbreit, Untergriff</t>
+  </si>
+  <si>
+    <t>LH Rudern, schulterbreit, Untergriff</t>
+  </si>
+  <si>
+    <t>Multipresse Rudern, schulterbreit, Untergriff</t>
+  </si>
+  <si>
+    <t>Steck Rudern, weit, Untergriff</t>
+  </si>
+  <si>
+    <t>Kabel Rudern, weit, Untergriff</t>
+  </si>
+  <si>
+    <t>KH Konzentrationscurls, Untergriff</t>
+  </si>
+  <si>
+    <t>Kabel Rudern, weit, Obergriff</t>
+  </si>
+  <si>
+    <t>KH Seitheben, vorgebeugt, Obergriff</t>
+  </si>
+  <si>
+    <t>Kabel Seitheben, vorgebeugt, Obergriff</t>
+  </si>
+  <si>
+    <t>LH Rudern, schulterbreit, Obergriff</t>
+  </si>
+  <si>
+    <t>Multipresse Rudern, wschulterbreiteit, Obergriff</t>
+  </si>
+  <si>
+    <t>PL Rudern, schulterbreit, Obergriff</t>
+  </si>
+  <si>
+    <t>Steck Rudern, schulterbreit, Obergriff</t>
+  </si>
+  <si>
+    <t>LH T-Bar Rudern eng</t>
+  </si>
+  <si>
+    <t>LH T-Bar Rudern schulterbreit</t>
   </si>
 </sst>
 </file>
@@ -958,7 +958,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1055,6 +1055,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1272,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D977"/>
+  <dimension ref="A1:D978"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1775,14 +1781,14 @@
       <c r="D36" s="2"/>
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>8</v>
@@ -1790,13 +1796,13 @@
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>8</v>
@@ -1804,13 +1810,13 @@
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="33" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>8</v>
@@ -1818,13 +1824,13 @@
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>8</v>
@@ -1832,13 +1838,13 @@
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>8</v>
@@ -1846,13 +1852,13 @@
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>8</v>
@@ -1860,13 +1866,13 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>56</v>
+        <v>238</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>8</v>
@@ -1874,13 +1880,13 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>8</v>
@@ -1888,13 +1894,13 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>8</v>
@@ -1902,13 +1908,13 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>32</v>
@@ -1916,13 +1922,13 @@
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>32</v>
@@ -1930,77 +1936,77 @@
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="7" t="s">
-        <v>64</v>
+      <c r="A49" s="34" t="s">
+        <v>247</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="7" t="s">
-        <v>67</v>
+      <c r="A50" s="34" t="s">
+        <v>248</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="7" t="s">
-        <v>68</v>
+      <c r="A51" s="34" t="s">
+        <v>249</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="7" t="s">
-        <v>69</v>
+      <c r="A52" s="34" t="s">
+        <v>250</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="7" t="s">
-        <v>70</v>
+      <c r="A53" s="34" t="s">
+        <v>244</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>8</v>
@@ -2008,13 +2014,13 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>71</v>
+        <v>239</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>8</v>
@@ -2022,13 +2028,13 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>73</v>
+        <v>240</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>8</v>
@@ -2036,13 +2042,13 @@
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>74</v>
+        <v>241</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>8</v>
@@ -2050,41 +2056,41 @@
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="7" t="s">
-        <v>76</v>
+      <c r="A58" s="34" t="s">
+        <v>252</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="7" t="s">
-        <v>77</v>
+      <c r="A59" s="34" t="s">
+        <v>251</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>8</v>
@@ -2092,27 +2098,27 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>32</v>
@@ -2120,13 +2126,13 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>32</v>
@@ -2134,13 +2140,13 @@
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>32</v>
@@ -2148,13 +2154,13 @@
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>32</v>
@@ -2162,13 +2168,13 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>32</v>
@@ -2176,13 +2182,13 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>32</v>
@@ -2190,13 +2196,13 @@
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>32</v>
@@ -2204,49 +2210,49 @@
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
+      <c r="A69" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>8</v>
-      </c>
+      <c r="A70" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="9" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C71" s="9" t="s">
-        <v>90</v>
+      <c r="C71" s="35" t="s">
+        <v>83</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>8</v>
@@ -2254,13 +2260,13 @@
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="9" t="s">
-        <v>90</v>
+      <c r="C72" s="35" t="s">
+        <v>83</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>8</v>
@@ -2268,13 +2274,13 @@
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="9" t="s">
-        <v>90</v>
+      <c r="C73" s="35" t="s">
+        <v>83</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>8</v>
@@ -2282,13 +2288,13 @@
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C74" s="9" t="s">
-        <v>90</v>
+      <c r="C74" s="35" t="s">
+        <v>83</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>8</v>
@@ -2296,13 +2302,13 @@
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="9" t="s">
-        <v>96</v>
+      <c r="C75" s="35" t="s">
+        <v>83</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>8</v>
@@ -2310,27 +2316,27 @@
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>32</v>
@@ -2338,13 +2344,13 @@
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>32</v>
@@ -2352,13 +2358,13 @@
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>32</v>
@@ -2366,13 +2372,13 @@
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>32</v>
@@ -2380,49 +2386,49 @@
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
+      <c r="A82" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>8</v>
-      </c>
+      <c r="A83" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="11" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D84" s="12" t="s">
         <v>8</v>
@@ -2430,13 +2436,13 @@
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="11" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D85" s="12" t="s">
         <v>8</v>
@@ -2444,13 +2450,13 @@
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="11" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>8</v>
@@ -2458,27 +2464,27 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="11" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B88" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C88" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>32</v>
@@ -2486,13 +2492,13 @@
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="B89" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C89" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D89" s="12" t="s">
         <v>32</v>
@@ -2500,13 +2506,13 @@
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="11" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B90" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C90" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>32</v>
@@ -2514,27 +2520,27 @@
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B91" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C91" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C91" s="11" t="s">
-        <v>50</v>
-      </c>
       <c r="D91" s="12" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>8</v>
@@ -2542,13 +2548,13 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="11" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>8</v>
@@ -2556,75 +2562,75 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="11" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D94" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B95" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C95" s="13"/>
-      <c r="D95" s="14" t="s">
-        <v>32</v>
+      <c r="A95" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>8</v>
+      <c r="A96" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
+      <c r="A97" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B98" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C98" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D98" s="14" t="s">
-        <v>32</v>
-      </c>
+      <c r="A98" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="13" t="s">
-        <v>123</v>
+        <v>245</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>32</v>
@@ -2632,13 +2638,13 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="13" t="s">
-        <v>124</v>
+        <v>246</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>32</v>
@@ -2646,13 +2652,13 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="13" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>32</v>
@@ -2660,13 +2666,13 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="13" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>32</v>
@@ -2674,49 +2680,49 @@
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="13" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
+      <c r="A104" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="B105" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C105" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="D105" s="16" t="s">
-        <v>32</v>
-      </c>
+      <c r="A105" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="15" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D106" s="16" t="s">
         <v>32</v>
@@ -2724,13 +2730,13 @@
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="15" t="s">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D107" s="16" t="s">
         <v>32</v>
@@ -2738,13 +2744,13 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="15" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D108" s="16" t="s">
         <v>32</v>
@@ -2752,13 +2758,13 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="15" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D109" s="16" t="s">
         <v>32</v>
@@ -2766,13 +2772,13 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="15" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D110" s="16" t="s">
         <v>32</v>
@@ -2780,13 +2786,13 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="15" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D111" s="16" t="s">
         <v>32</v>
@@ -2794,13 +2800,13 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="15" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D112" s="16" t="s">
         <v>32</v>
@@ -2808,13 +2814,13 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="15" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D113" s="16" t="s">
         <v>32</v>
@@ -2822,13 +2828,13 @@
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="15" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D114" s="16" t="s">
         <v>32</v>
@@ -2836,13 +2842,13 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="15" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D115" s="16" t="s">
         <v>32</v>
@@ -2850,13 +2856,13 @@
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="15" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D116" s="16" t="s">
         <v>32</v>
@@ -2864,13 +2870,13 @@
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="15" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D117" s="16" t="s">
         <v>32</v>
@@ -2878,13 +2884,13 @@
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="15" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D118" s="16" t="s">
         <v>32</v>
@@ -2892,13 +2898,13 @@
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="15" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D119" s="16" t="s">
         <v>32</v>
@@ -2906,13 +2912,13 @@
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="15" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D120" s="16" t="s">
         <v>32</v>
@@ -2920,13 +2926,13 @@
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="15" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D121" s="16" t="s">
         <v>32</v>
@@ -2934,13 +2940,13 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D122" s="16" t="s">
         <v>32</v>
@@ -2948,13 +2954,13 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="15" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D123" s="16" t="s">
         <v>32</v>
@@ -2962,13 +2968,13 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="15" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D124" s="16" t="s">
         <v>32</v>
@@ -2976,13 +2982,13 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="15" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D125" s="16" t="s">
         <v>32</v>
@@ -2990,13 +2996,13 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="15" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D126" s="16" t="s">
         <v>32</v>
@@ -3004,49 +3010,49 @@
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="15" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D127" s="16" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
+      <c r="A128" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B128" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C128" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D128" s="16" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="B129" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="C129" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="D129" s="18" t="s">
-        <v>32</v>
-      </c>
+      <c r="A129" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="17" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C130" s="17" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D130" s="18" t="s">
         <v>32</v>
@@ -3054,13 +3060,13 @@
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="17" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D131" s="18" t="s">
         <v>32</v>
@@ -3068,13 +3074,13 @@
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="17" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D132" s="18" t="s">
         <v>32</v>
@@ -3082,13 +3088,13 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="17" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C133" s="17" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D133" s="18" t="s">
         <v>32</v>
@@ -3096,13 +3102,13 @@
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="17" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D134" s="18" t="s">
         <v>32</v>
@@ -3110,13 +3116,13 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="17" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D135" s="18" t="s">
         <v>32</v>
@@ -3124,13 +3130,13 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="17" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D136" s="18" t="s">
         <v>32</v>
@@ -3138,13 +3144,13 @@
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="17" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D137" s="18" t="s">
         <v>32</v>
@@ -3152,13 +3158,13 @@
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="17" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C138" s="17" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D138" s="18" t="s">
         <v>32</v>
@@ -3166,13 +3172,13 @@
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="17" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D139" s="18" t="s">
         <v>32</v>
@@ -3180,13 +3186,13 @@
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="17" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D140" s="18" t="s">
         <v>32</v>
@@ -3194,27 +3200,27 @@
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="17" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="D141" s="18" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="17" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D142" s="18" t="s">
         <v>8</v>
@@ -3222,13 +3228,13 @@
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="17" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D143" s="18" t="s">
         <v>8</v>
@@ -3236,49 +3242,49 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="17" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D144" s="18" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
+      <c r="A145" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B145" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C145" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="D145" s="18" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B146" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="C146" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D146" s="20" t="s">
-        <v>32</v>
-      </c>
+      <c r="A146" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="19" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="B147" s="19" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D147" s="20" t="s">
         <v>32</v>
@@ -3286,13 +3292,13 @@
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="19" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="B148" s="19" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D148" s="20" t="s">
         <v>32</v>
@@ -3300,13 +3306,13 @@
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="19" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B149" s="19" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="D149" s="20" t="s">
         <v>32</v>
@@ -3314,13 +3320,13 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="19" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="B150" s="19" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D150" s="20" t="s">
         <v>32</v>
@@ -3328,13 +3334,13 @@
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="19" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="B151" s="19" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D151" s="20" t="s">
         <v>32</v>
@@ -3342,13 +3348,13 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="19" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="B152" s="19" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C152" s="19" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D152" s="20" t="s">
         <v>32</v>
@@ -3356,49 +3362,49 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="19" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B153" s="19" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D153" s="20" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B154" s="2"/>
-      <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
+      <c r="A154" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B154" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C154" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D154" s="20" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="B155" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="C155" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D155" s="22" t="s">
-        <v>8</v>
-      </c>
+      <c r="A155" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="21" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C156" s="21" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D156" s="22" t="s">
         <v>8</v>
@@ -3406,13 +3412,13 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="21" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C157" s="21" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="D157" s="22" t="s">
         <v>8</v>
@@ -3420,13 +3426,13 @@
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="21" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D158" s="22" t="s">
         <v>8</v>
@@ -3434,13 +3440,13 @@
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="21" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C159" s="21" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="D159" s="22" t="s">
         <v>8</v>
@@ -3448,13 +3454,13 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="21" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C160" s="21" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D160" s="22" t="s">
         <v>8</v>
@@ -3462,13 +3468,13 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="21" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C161" s="21" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="D161" s="22" t="s">
         <v>8</v>
@@ -3476,13 +3482,13 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="21" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D162" s="22" t="s">
         <v>8</v>
@@ -3490,13 +3496,13 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="21" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D163" s="22" t="s">
         <v>8</v>
@@ -3504,13 +3510,13 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="21" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D164" s="22" t="s">
         <v>8</v>
@@ -3518,13 +3524,13 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="21" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>8</v>
@@ -3532,13 +3538,13 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="21" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D166" s="22" t="s">
         <v>8</v>
@@ -3546,13 +3552,13 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="21" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D167" s="22" t="s">
         <v>8</v>
@@ -3560,63 +3566,63 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="21" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="21" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="B169" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D169" s="22" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B170" s="2"/>
-      <c r="C170" s="2"/>
-      <c r="D170" s="2"/>
+      <c r="A170" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B170" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C170" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D170" s="22" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="B171" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="C171" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="D171" s="24" t="s">
-        <v>8</v>
-      </c>
+      <c r="A171" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="23" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="B172" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C172" s="23" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D172" s="24" t="s">
         <v>8</v>
@@ -3624,13 +3630,13 @@
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="23" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="B173" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C173" s="23" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D173" s="24" t="s">
         <v>8</v>
@@ -3638,13 +3644,13 @@
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="23" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="B174" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C174" s="23" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="D174" s="24" t="s">
         <v>8</v>
@@ -3652,13 +3658,13 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="23" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="B175" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C175" s="23" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="D175" s="24" t="s">
         <v>8</v>
@@ -3666,13 +3672,13 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="23" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="B176" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D176" s="24" t="s">
         <v>8</v>
@@ -3680,27 +3686,27 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="23" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B177" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C177" s="23" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="D177" s="24" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="23" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="B178" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C178" s="23" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D178" s="24" t="s">
         <v>32</v>
@@ -3708,13 +3714,13 @@
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="23" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="B179" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C179" s="23" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D179" s="24" t="s">
         <v>32</v>
@@ -3722,13 +3728,13 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="23" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="B180" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C180" s="23" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D180" s="24" t="s">
         <v>32</v>
@@ -3736,13 +3742,13 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="23" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="B181" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C181" s="23" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D181" s="24" t="s">
         <v>32</v>
@@ -3750,13 +3756,13 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="23" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="B182" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C182" s="23" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D182" s="24" t="s">
         <v>32</v>
@@ -3764,49 +3770,49 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="23" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="B183" s="23" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C183" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="D183" s="24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="B184" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="D183" s="24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B184" s="2"/>
-      <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
+      <c r="C184" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="D184" s="24" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="B185" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C185" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="D185" s="26" t="s">
-        <v>8</v>
-      </c>
+      <c r="A185" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="25" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="B186" s="25" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C186" s="25" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="D186" s="26" t="s">
         <v>8</v>
@@ -3814,13 +3820,13 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="25" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="B187" s="25" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C187" s="25" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D187" s="26" t="s">
         <v>8</v>
@@ -3828,13 +3834,13 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="25" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="B188" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C188" s="25" t="s">
         <v>188</v>
-      </c>
-      <c r="C188" s="25" t="s">
-        <v>204</v>
       </c>
       <c r="D188" s="26" t="s">
         <v>8</v>
@@ -3842,13 +3848,13 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="25" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="B189" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C189" s="25" t="s">
         <v>188</v>
-      </c>
-      <c r="C189" s="25" t="s">
-        <v>204</v>
       </c>
       <c r="D189" s="26" t="s">
         <v>8</v>
@@ -3856,27 +3862,27 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="25" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="B190" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C190" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="C190" s="25" t="s">
-        <v>204</v>
-      </c>
       <c r="D190" s="26" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="25" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="B191" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C191" s="25" t="s">
         <v>188</v>
-      </c>
-      <c r="C191" s="25" t="s">
-        <v>204</v>
       </c>
       <c r="D191" s="26" t="s">
         <v>32</v>
@@ -3884,13 +3890,13 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="25" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="B192" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C192" s="25" t="s">
         <v>188</v>
-      </c>
-      <c r="C192" s="25" t="s">
-        <v>204</v>
       </c>
       <c r="D192" s="26" t="s">
         <v>32</v>
@@ -3898,10 +3904,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="25" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="B193" s="25" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C193" s="25" t="s">
         <v>188</v>
@@ -3912,85 +3918,85 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="25" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="B194" s="25" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C194" s="25" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D194" s="26" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B195" s="2"/>
-      <c r="C195" s="2"/>
-      <c r="D195" s="2"/>
+      <c r="A195" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="B195" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C195" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="D195" s="26" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="B196" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="C196" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="D196" s="28" t="s">
-        <v>32</v>
-      </c>
+      <c r="A196" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="27" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="B197" s="27" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C197" s="27" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D197" s="28" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
+      <c r="A198" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="B198" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="C198" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D198" s="28" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="B199" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="C199" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="D199" s="30" t="s">
-        <v>32</v>
-      </c>
+      <c r="A199" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="29" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="B200" s="29" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C200" s="29" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D200" s="30" t="s">
         <v>32</v>
@@ -3998,13 +4004,13 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="29" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="B201" s="29" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C201" s="29" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D201" s="30" t="s">
         <v>32</v>
@@ -4012,13 +4018,13 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="29" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="B202" s="29" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C202" s="29" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D202" s="30" t="s">
         <v>32</v>
@@ -4026,13 +4032,13 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="29" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="B203" s="29" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C203" s="29" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D203" s="30" t="s">
         <v>32</v>
@@ -4040,13 +4046,13 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="29" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="B204" s="29" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C204" s="29" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D204" s="30" t="s">
         <v>32</v>
@@ -4054,13 +4060,13 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="29" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="B205" s="29" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C205" s="29" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D205" s="30" t="s">
         <v>32</v>
@@ -4068,13 +4074,13 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="29" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="B206" s="29" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C206" s="29" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D206" s="30" t="s">
         <v>32</v>
@@ -4082,49 +4088,49 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="29" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B207" s="29" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C207" s="29" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D207" s="30" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B208" s="2"/>
-      <c r="C208" s="2"/>
-      <c r="D208" s="2"/>
+      <c r="A208" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="B208" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="C208" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D208" s="30" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="B209" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C209" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="D209" s="32" t="s">
-        <v>32</v>
-      </c>
+      <c r="A209" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B209" s="2"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="31" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="B210" s="31" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C210" s="31" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D210" s="32" t="s">
         <v>32</v>
@@ -4132,13 +4138,13 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="31" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B211" s="31" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C211" s="31" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D211" s="32" t="s">
         <v>32</v>
@@ -4146,19 +4152,32 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="31" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B212" s="31" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C212" s="31" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D212" s="32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="B213" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="C213" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D213" s="32" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4923,6 +4942,7 @@
     <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F63D24-631E-1245-97A2-2A05D2850843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377ABF86-9E4F-F446-A379-204BDA6CCFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Übungsliste" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="255">
   <si>
     <t>Übung</t>
   </si>
@@ -60,9 +60,6 @@
     <t>KH Schrägbankdrücken</t>
   </si>
   <si>
-    <t>PL Schrägbankdrücken</t>
-  </si>
-  <si>
     <t>Steck Schrägbankdrücken</t>
   </si>
   <si>
@@ -75,9 +72,6 @@
     <t>KH Flachbankdrücken</t>
   </si>
   <si>
-    <t>PL Flachbankdrücken</t>
-  </si>
-  <si>
     <t>Steck Flachbankdrücken</t>
   </si>
   <si>
@@ -93,9 +87,6 @@
     <t>KH Flachbankdrücken, neutral</t>
   </si>
   <si>
-    <t>PL Flachbankdrücken, neutral</t>
-  </si>
-  <si>
     <t>Steck Flachbankdrücken, neutral</t>
   </si>
   <si>
@@ -108,9 +99,6 @@
     <t>KH Negativbankdrücken</t>
   </si>
   <si>
-    <t>PL Negativbankdrücken</t>
-  </si>
-  <si>
     <t>LH Guillotine Bankdrücken</t>
   </si>
   <si>
@@ -126,9 +114,6 @@
     <t>Iso</t>
   </si>
   <si>
-    <t>PL Fliegende</t>
-  </si>
-  <si>
     <t>Steck Fliegende</t>
   </si>
   <si>
@@ -150,9 +135,6 @@
     <t>Kabel Überzüge</t>
   </si>
   <si>
-    <t>PL Dips (Brustbetont)</t>
-  </si>
-  <si>
     <t>Bank Dips (Brustbetont)</t>
   </si>
   <si>
@@ -183,12 +165,6 @@
     <t>Bizeps, Hintere Schulter, Oberer Rücken</t>
   </si>
   <si>
-    <t>Kabel Latziehen in den Nacken, Obergriff, weit</t>
-  </si>
-  <si>
-    <t>Kabel Latziehen, eng, neutral</t>
-  </si>
-  <si>
     <t>Bizeps</t>
   </si>
   <si>
@@ -222,9 +198,6 @@
     <t>Lat, Bizeps</t>
   </si>
   <si>
-    <t>PL T-Bar Rudern</t>
-  </si>
-  <si>
     <t>LH Shruggs</t>
   </si>
   <si>
@@ -267,9 +240,6 @@
     <t>KH Frontdrücken</t>
   </si>
   <si>
-    <t>PL Frontdrücken</t>
-  </si>
-  <si>
     <t>Steck Frontdrücken</t>
   </si>
   <si>
@@ -312,9 +282,6 @@
     <t>Multipresse Nackendrücken</t>
   </si>
   <si>
-    <t>PL Nackendrücken</t>
-  </si>
-  <si>
     <t>Steck Nackendrücken</t>
   </si>
   <si>
@@ -324,9 +291,6 @@
     <t>Vordere Schulter, Hintere Schulter</t>
   </si>
   <si>
-    <t>PL Seitheben</t>
-  </si>
-  <si>
     <t>Steck Seitheben</t>
   </si>
   <si>
@@ -357,9 +321,6 @@
     <t>KH Reverse Flys</t>
   </si>
   <si>
-    <t>PL Reverse Flys</t>
-  </si>
-  <si>
     <t>Steck Reverse Flys</t>
   </si>
   <si>
@@ -390,9 +351,6 @@
     <t>KH Curls, Untergriff</t>
   </si>
   <si>
-    <t>PL Curls, Untergriff</t>
-  </si>
-  <si>
     <t>Steck Curls, Untergriff</t>
   </si>
   <si>
@@ -405,9 +363,6 @@
     <t>Kabel Superman-Curls</t>
   </si>
   <si>
-    <t>PL Scott Curls, Maschine</t>
-  </si>
-  <si>
     <t>Steck Scott Curls, Maschine</t>
   </si>
   <si>
@@ -489,9 +444,6 @@
     <t>Brust, Vordere Schulter</t>
   </si>
   <si>
-    <t>PL Dips (Trizepsbetont)</t>
-  </si>
-  <si>
     <t>Steck Dips (Trizepsbetont)</t>
   </si>
   <si>
@@ -549,15 +501,9 @@
     <t>Multipresse Frontkniebeugen</t>
   </si>
   <si>
-    <t>PL Beinpresse</t>
-  </si>
-  <si>
     <t>Steck Beinpresse</t>
   </si>
   <si>
-    <t>PL Hackenschmidt-Kniebeugen</t>
-  </si>
-  <si>
     <t>Glutes, Adduktoren</t>
   </si>
   <si>
@@ -567,21 +513,6 @@
     <t>KH Ausfallschritte</t>
   </si>
   <si>
-    <t>LH Splitsquats</t>
-  </si>
-  <si>
-    <t>KH Splitsquats</t>
-  </si>
-  <si>
-    <t>LH Bulgarian Splitsquats</t>
-  </si>
-  <si>
-    <t>KH Bulgarian Splitsquats</t>
-  </si>
-  <si>
-    <t>PL Beinstrecken</t>
-  </si>
-  <si>
     <t>Steck Beinstrecken</t>
   </si>
   <si>
@@ -612,24 +543,15 @@
     <t>LH Good Mornings</t>
   </si>
   <si>
-    <t>PL Beinbeugen, liegend</t>
-  </si>
-  <si>
     <t>Waden</t>
   </si>
   <si>
     <t>Steck Beinbeugen, liegend</t>
   </si>
   <si>
-    <t>PL Beinbeugen, stehend</t>
-  </si>
-  <si>
     <t>Steck Beinbeugen, stehend</t>
   </si>
   <si>
-    <t>PL Beinbeugen, sitzend</t>
-  </si>
-  <si>
     <t>Steck Beinbeugen, sitzend</t>
   </si>
   <si>
@@ -657,9 +579,6 @@
     <t>Multipresse Hip Thrust</t>
   </si>
   <si>
-    <t>PL Hip Thrust</t>
-  </si>
-  <si>
     <t>Kabel Kickbacks</t>
   </si>
   <si>
@@ -669,18 +588,12 @@
     <t>KH Back Extensions, horizontal</t>
   </si>
   <si>
-    <t>PL Abduktionen</t>
-  </si>
-  <si>
     <t>Steck Abduktionen</t>
   </si>
   <si>
     <t>■ ADDUKTOREN</t>
   </si>
   <si>
-    <t>PL Adduktionen</t>
-  </si>
-  <si>
     <t>Adduktoren</t>
   </si>
   <si>
@@ -699,9 +612,6 @@
     <t>KH Wadenheben, stehend</t>
   </si>
   <si>
-    <t>PL Wadenheben, stehend</t>
-  </si>
-  <si>
     <t>Steck Wadenheben, stehend</t>
   </si>
   <si>
@@ -711,9 +621,6 @@
     <t>Multipresse Wadenheben, sitzend</t>
   </si>
   <si>
-    <t>PL Wadenheben, sitzend</t>
-  </si>
-  <si>
     <t>Steck Wadenheben, sitzend</t>
   </si>
   <si>
@@ -729,21 +636,12 @@
     <t>Beinheben</t>
   </si>
   <si>
-    <t>Planks</t>
-  </si>
-  <si>
-    <t>Sideplanks</t>
-  </si>
-  <si>
     <t>Klimmzug, Obergriff, weit</t>
   </si>
   <si>
     <t>Klimmzug, Untergriff, schulterbreit</t>
   </si>
   <si>
-    <t>Kabel Latziehen, schulterbreit, Untergriff</t>
-  </si>
-  <si>
     <t>LH Rudern, schulterbreit, Untergriff</t>
   </si>
   <si>
@@ -753,9 +651,6 @@
     <t>Steck Rudern, weit, Untergriff</t>
   </si>
   <si>
-    <t>Kabel Rudern, weit, Untergriff</t>
-  </si>
-  <si>
     <t>KH Konzentrationscurls, Untergriff</t>
   </si>
   <si>
@@ -774,9 +669,6 @@
     <t>Multipresse Rudern, wschulterbreiteit, Obergriff</t>
   </si>
   <si>
-    <t>PL Rudern, schulterbreit, Obergriff</t>
-  </si>
-  <si>
     <t>Steck Rudern, schulterbreit, Obergriff</t>
   </si>
   <si>
@@ -784,6 +676,120 @@
   </si>
   <si>
     <t>LH T-Bar Rudern schulterbreit</t>
+  </si>
+  <si>
+    <t>KH Commerfordcurls</t>
+  </si>
+  <si>
+    <t>KH Zottman Curls</t>
+  </si>
+  <si>
+    <t>PlateLoaded Schrägbankdrücken</t>
+  </si>
+  <si>
+    <t>PlateLoaded Flachbankdrücken</t>
+  </si>
+  <si>
+    <t>PlateLoaded Flachbankdrücken, neutral</t>
+  </si>
+  <si>
+    <t>PlateLoaded Negativbankdrücken</t>
+  </si>
+  <si>
+    <t>PlateLoaded Fliegende</t>
+  </si>
+  <si>
+    <t>PlateLoaded Dips (Brustbetont)</t>
+  </si>
+  <si>
+    <t>PlateLoaded Rudern, schulterbreit, Obergriff</t>
+  </si>
+  <si>
+    <t>PlateLoaded T-Bar Rudern</t>
+  </si>
+  <si>
+    <t>PlateLoaded Frontdrücken</t>
+  </si>
+  <si>
+    <t>PlateLoaded Nackendrücken</t>
+  </si>
+  <si>
+    <t>PlateLoaded Seitheben</t>
+  </si>
+  <si>
+    <t>PlateLoaded Reverse Flys</t>
+  </si>
+  <si>
+    <t>PlateLoaded Scott Curls, Maschine</t>
+  </si>
+  <si>
+    <t>PlateLoaded Dips (Trizepsbetont)</t>
+  </si>
+  <si>
+    <t>PlateLoaded Beinpresse</t>
+  </si>
+  <si>
+    <t>PlateLoaded Hackenschmidt-Kniebeugen</t>
+  </si>
+  <si>
+    <t>LH SPlateLoadeditsquats</t>
+  </si>
+  <si>
+    <t>KH SPlateLoadeditsquats</t>
+  </si>
+  <si>
+    <t>LH Bulgarian SPlateLoadeditsquats</t>
+  </si>
+  <si>
+    <t>KH Bulgarian SPlateLoadeditsquats</t>
+  </si>
+  <si>
+    <t>PlateLoaded Beinstrecken</t>
+  </si>
+  <si>
+    <t>PlateLoaded Beinbeugen, liegend</t>
+  </si>
+  <si>
+    <t>PlateLoaded Beinbeugen, stehend</t>
+  </si>
+  <si>
+    <t>PlateLoaded Beinbeugen, sitzend</t>
+  </si>
+  <si>
+    <t>PlateLoaded Hip Thrust</t>
+  </si>
+  <si>
+    <t>PlateLoaded Abduktionen</t>
+  </si>
+  <si>
+    <t>PlateLoaded Adduktionen</t>
+  </si>
+  <si>
+    <t>PlateLoaded Wadenheben, stehend</t>
+  </si>
+  <si>
+    <t>PlateLoaded Wadenheben, sitzend</t>
+  </si>
+  <si>
+    <t>PlateLoadedanks</t>
+  </si>
+  <si>
+    <t>SidePlateLoadedanks</t>
+  </si>
+  <si>
+    <t>Latziehen in den Nacken, Obergriff, weit</t>
+  </si>
+  <si>
+    <t>Latziehen, eng, neutral</t>
+  </si>
+  <si>
+    <t>Latziehen, schulterbreit, Untergriff</t>
+  </si>
+  <si>
+    <t>Rudern Multipresse, Brustgestützt, Obergriff</t>
+  </si>
+  <si>
+    <t>KHRudern, Brustgestützt, Obergriff</t>
   </si>
 </sst>
 </file>
@@ -958,7 +964,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1062,6 +1068,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1278,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D978"/>
+  <dimension ref="A1:D980"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1354,7 +1372,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>6</v>
@@ -1368,7 +1386,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
@@ -1382,7 +1400,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>6</v>
@@ -1396,7 +1414,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>6</v>
@@ -1410,7 +1428,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>6</v>
@@ -1424,7 +1442,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>6</v>
@@ -1438,7 +1456,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>6</v>
@@ -1452,13 +1470,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>8</v>
@@ -1466,13 +1484,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>8</v>
@@ -1480,7 +1498,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>6</v>
@@ -1494,7 +1512,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>221</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>6</v>
@@ -1508,7 +1526,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>6</v>
@@ -1522,7 +1540,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>6</v>
@@ -1536,7 +1554,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>6</v>
@@ -1550,7 +1568,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
@@ -1564,7 +1582,7 @@
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>6</v>
@@ -1578,7 +1596,7 @@
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>6</v>
@@ -1592,7 +1610,7 @@
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>6</v>
@@ -1606,125 +1624,125 @@
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>33</v>
+        <v>223</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>41</v>
+        <v>224</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>8</v>
@@ -1732,13 +1750,13 @@
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>8</v>
@@ -1746,13 +1764,13 @@
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>8</v>
@@ -1760,13 +1778,13 @@
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>8</v>
@@ -1774,7 +1792,7 @@
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -1782,13 +1800,13 @@
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="33" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>8</v>
@@ -1796,13 +1814,13 @@
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>8</v>
@@ -1810,13 +1828,13 @@
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="33" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>8</v>
@@ -1824,55 +1842,55 @@
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B41" s="5" t="s">
+      <c r="D42" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>8</v>
@@ -1880,13 +1898,13 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>8</v>
@@ -1894,13 +1912,13 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>8</v>
@@ -1908,35 +1926,35 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -1944,13 +1962,13 @@
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="34" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>8</v>
@@ -1958,13 +1976,13 @@
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="34" t="s">
-        <v>248</v>
+        <v>213</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>8</v>
@@ -1972,13 +1990,13 @@
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="34" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>8</v>
@@ -1986,13 +2004,13 @@
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="34" t="s">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>8</v>
@@ -2000,13 +2018,13 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="34" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>8</v>
@@ -2014,13 +2032,13 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>8</v>
@@ -2028,13 +2046,13 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>8</v>
@@ -2042,27 +2060,27 @@
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="7" t="s">
-        <v>242</v>
+      <c r="A57" s="34" t="s">
+        <v>254</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>8</v>
@@ -2070,13 +2088,13 @@
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>8</v>
@@ -2084,27 +2102,27 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="34" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="7" t="s">
-        <v>65</v>
+      <c r="A60" s="34" t="s">
+        <v>215</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>8</v>
@@ -2112,161 +2130,161 @@
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>66</v>
+        <v>226</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B66" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C66" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="D66" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B67" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C67" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="D67" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B68" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="D68" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B69" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C69" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="D69" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
+      <c r="A70" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>8</v>
-      </c>
+      <c r="A71" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>8</v>
@@ -2274,13 +2292,13 @@
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>8</v>
@@ -2288,13 +2306,13 @@
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>8</v>
@@ -2302,13 +2320,13 @@
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="s">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>8</v>
@@ -2316,13 +2334,13 @@
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>83</v>
+        <v>27</v>
+      </c>
+      <c r="C76" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>8</v>
@@ -2330,119 +2348,119 @@
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
+      <c r="A83" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>8</v>
-      </c>
+      <c r="A84" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D85" s="12" t="s">
         <v>8</v>
@@ -2450,13 +2468,13 @@
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="11" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>8</v>
@@ -2464,13 +2482,13 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="11" t="s">
-        <v>96</v>
+        <v>228</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D87" s="12" t="s">
         <v>8</v>
@@ -2478,83 +2496,83 @@
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="11" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="11" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>8</v>
@@ -2562,13 +2580,13 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="11" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D94" s="12" t="s">
         <v>8</v>
@@ -2576,665 +2594,665 @@
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="11" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D95" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B96" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14" t="s">
-        <v>32</v>
+      <c r="A96" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B97" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>8</v>
+      <c r="A97" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C97" s="13"/>
+      <c r="D97" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
+      <c r="A98" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="B99" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C99" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D99" s="14" t="s">
-        <v>32</v>
-      </c>
+      <c r="A99" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="13" t="s">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="13" t="s">
-        <v>109</v>
+        <v>211</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="13" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="13" t="s">
-        <v>111</v>
+        <v>230</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="13" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C104" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B105" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D104" s="14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
+      <c r="C105" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B106" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C106" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D106" s="16" t="s">
-        <v>32</v>
-      </c>
+      <c r="A106" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="15" t="s">
-        <v>243</v>
+        <v>101</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="15" t="s">
-        <v>116</v>
+        <v>208</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="15" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="15" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="B111" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C111" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D111" s="16" t="s">
-        <v>32</v>
+      <c r="A111" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="B111" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C111" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="D111" s="37" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="15" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="15" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="15" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="15" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D115" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="15" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="15" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="15" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D118" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="15" t="s">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="15" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="15" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="15" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="15" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="15" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="15" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="15" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="15" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
+      <c r="A129" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B129" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C129" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D129" s="16" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="B130" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="C130" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="D130" s="18" t="s">
-        <v>32</v>
-      </c>
+      <c r="A130" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="17" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D131" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="17" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D132" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="17" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C133" s="17" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="17" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D134" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="17" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="17" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D136" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="17" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D137" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="17" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C138" s="17" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D138" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="17" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D139" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="17" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D140" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="17" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D141" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="17" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="D142" s="18" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="17" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D143" s="18" t="s">
         <v>8</v>
@@ -3242,13 +3260,13 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="17" t="s">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D144" s="18" t="s">
         <v>8</v>
@@ -3256,183 +3274,183 @@
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="17" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D145" s="18" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
+      <c r="A146" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B146" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C146" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D146" s="18" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="B147" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="C147" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D147" s="20" t="s">
-        <v>32</v>
-      </c>
+      <c r="A147" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="19" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="B148" s="19" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D148" s="20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="19" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="B149" s="19" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D149" s="20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="19" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="B150" s="19" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="D150" s="20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="19" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="B151" s="19" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D151" s="20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="19" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="B152" s="19" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C152" s="19" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D152" s="20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="19" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="B153" s="19" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D153" s="20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="19" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="B154" s="19" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C154" s="19" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D154" s="20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B155" s="2"/>
-      <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
+      <c r="A155" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B155" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C155" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D155" s="20" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="B156" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="C156" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="D156" s="22" t="s">
-        <v>8</v>
+      <c r="A156" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="B156" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C156" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D156" s="39" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="B157" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="C157" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="D157" s="22" t="s">
-        <v>8</v>
-      </c>
+      <c r="A157" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="21" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="D158" s="22" t="s">
         <v>8</v>
@@ -3440,13 +3458,13 @@
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="21" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C159" s="21" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="D159" s="22" t="s">
         <v>8</v>
@@ -3454,13 +3472,13 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="21" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C160" s="21" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D160" s="22" t="s">
         <v>8</v>
@@ -3468,13 +3486,13 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="21" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C161" s="21" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D161" s="22" t="s">
         <v>8</v>
@@ -3482,13 +3500,13 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="21" t="s">
-        <v>176</v>
+        <v>233</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="D162" s="22" t="s">
         <v>8</v>
@@ -3496,13 +3514,13 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="21" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="D163" s="22" t="s">
         <v>8</v>
@@ -3510,13 +3528,13 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="21" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="D164" s="22" t="s">
         <v>8</v>
@@ -3524,13 +3542,13 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="21" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>8</v>
@@ -3538,13 +3556,13 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="21" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="D166" s="22" t="s">
         <v>8</v>
@@ -3552,13 +3570,13 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="21" t="s">
-        <v>182</v>
+        <v>235</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="D167" s="22" t="s">
         <v>8</v>
@@ -3566,13 +3584,13 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="21" t="s">
-        <v>183</v>
+        <v>236</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="D168" s="22" t="s">
         <v>8</v>
@@ -3580,77 +3598,77 @@
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="21" t="s">
-        <v>184</v>
+        <v>237</v>
       </c>
       <c r="B169" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D169" s="22" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="21" t="s">
-        <v>185</v>
+        <v>238</v>
       </c>
       <c r="B170" s="21" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D170" s="22" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B171" s="2"/>
-      <c r="C171" s="2"/>
-      <c r="D171" s="2"/>
+      <c r="A171" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="B171" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C171" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D171" s="22" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="B172" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="C172" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="D172" s="24" t="s">
-        <v>8</v>
+      <c r="A172" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B172" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C172" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D172" s="22" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="B173" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="C173" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="D173" s="24" t="s">
-        <v>8</v>
-      </c>
+      <c r="A173" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="23" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="B174" s="23" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C174" s="23" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="D174" s="24" t="s">
         <v>8</v>
@@ -3658,13 +3676,13 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="23" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="B175" s="23" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C175" s="23" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="D175" s="24" t="s">
         <v>8</v>
@@ -3672,13 +3690,13 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="23" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="B176" s="23" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="D176" s="24" t="s">
         <v>8</v>
@@ -3686,13 +3704,13 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="23" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="B177" s="23" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C177" s="23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D177" s="24" t="s">
         <v>8</v>
@@ -3700,147 +3718,147 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="23" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="B178" s="23" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C178" s="23" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="D178" s="24" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="23" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="B179" s="23" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C179" s="23" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="D179" s="24" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="23" t="s">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="B180" s="23" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C180" s="23" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="D180" s="24" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="23" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="B181" s="23" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C181" s="23" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="D181" s="24" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="23" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="B182" s="23" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C182" s="23" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="D182" s="24" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="23" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="B183" s="23" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C183" s="23" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="D183" s="24" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="23" t="s">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="B184" s="23" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C184" s="23" t="s">
         <v>172</v>
       </c>
       <c r="D184" s="24" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B185" s="2"/>
-      <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
+      <c r="A185" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="B185" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C185" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="D185" s="24" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="B186" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C186" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D186" s="26" t="s">
-        <v>8</v>
+      <c r="A186" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="B186" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C186" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="D186" s="24" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="B187" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C187" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="D187" s="26" t="s">
-        <v>8</v>
-      </c>
+      <c r="A187" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="25" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="B188" s="25" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C188" s="25" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D188" s="26" t="s">
         <v>8</v>
@@ -3848,13 +3866,13 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="25" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="B189" s="25" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C189" s="25" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D189" s="26" t="s">
         <v>8</v>
@@ -3862,13 +3880,13 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="25" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="B190" s="25" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C190" s="25" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="D190" s="26" t="s">
         <v>8</v>
@@ -3876,310 +3894,336 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="25" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="B191" s="25" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="D191" s="26" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="25" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="B192" s="25" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="D192" s="26" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="25" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="B193" s="25" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C193" s="25" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="D193" s="26" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="25" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="B194" s="25" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C194" s="25" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D194" s="26" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="25" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="B195" s="25" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C195" s="25" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D195" s="26" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B196" s="2"/>
-      <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
+      <c r="A196" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="B196" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C196" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="D196" s="26" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B197" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="C197" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D197" s="28" t="s">
-        <v>32</v>
+      <c r="A197" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B197" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C197" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="D197" s="26" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="B198" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="C198" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D198" s="28" t="s">
-        <v>32</v>
-      </c>
+      <c r="A198" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B199" s="2"/>
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
+      <c r="A199" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="B199" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="C199" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D199" s="28" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="B200" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="C200" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D200" s="30" t="s">
-        <v>32</v>
+      <c r="A200" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="B200" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="C200" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D200" s="28" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="B201" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="C201" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D201" s="30" t="s">
-        <v>32</v>
-      </c>
+      <c r="A201" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B201" s="2"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="29" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="B202" s="29" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C202" s="29" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D202" s="30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="29" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="B203" s="29" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C203" s="29" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D203" s="30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="29" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="B204" s="29" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C204" s="29" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D204" s="30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="29" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="B205" s="29" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C205" s="29" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D205" s="30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="29" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="B206" s="29" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C206" s="29" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D206" s="30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="29" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="B207" s="29" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C207" s="29" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D207" s="30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="29" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="B208" s="29" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C208" s="29" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D208" s="30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B209" s="2"/>
-      <c r="C209" s="2"/>
-      <c r="D209" s="2"/>
+      <c r="A209" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="B209" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="C209" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="D209" s="30" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="B210" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="C210" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D210" s="32" t="s">
-        <v>32</v>
+      <c r="A210" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B210" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="C210" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="D210" s="30" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="31" t="s">
-        <v>233</v>
-      </c>
-      <c r="B211" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="C211" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D211" s="32" t="s">
-        <v>32</v>
-      </c>
+      <c r="A211" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="31" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="B212" s="31" t="s">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="C212" s="31" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D212" s="32" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="31" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="B213" s="31" t="s">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="C213" s="31" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D213" s="32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="B214" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="C214" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="D214" s="32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="B215" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="C215" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="D215" s="32" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4943,6 +4987,8 @@
     <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377ABF86-9E4F-F446-A379-204BDA6CCFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F7A40C-1FAD-7244-8577-10FE1FBBC625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,9 +159,6 @@
     <t>Oberer Rücken, Bizeps</t>
   </si>
   <si>
-    <t>Kabel Latziehen zur Brust, Obergriff</t>
-  </si>
-  <si>
     <t>Bizeps, Hintere Schulter, Oberer Rücken</t>
   </si>
   <si>
@@ -790,6 +787,9 @@
   </si>
   <si>
     <t>KHRudern, Brustgestützt, Obergriff</t>
+  </si>
+  <si>
+    <t>Latziehen zur Brust, Obergriff</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>6</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>6</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>6</v>
@@ -1582,7 +1582,7 @@
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>6</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>6</v>
@@ -1736,7 +1736,7 @@
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>6</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>40</v>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="33" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>40</v>
@@ -1841,14 +1841,14 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
-        <v>44</v>
+      <c r="A40" s="33" t="s">
+        <v>254</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>8</v>
@@ -1856,7 +1856,7 @@
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>40</v>
@@ -1870,13 +1870,13 @@
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="33" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>8</v>
@@ -1884,13 +1884,13 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>8</v>
@@ -1898,13 +1898,13 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>8</v>
@@ -1912,13 +1912,13 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>8</v>
@@ -1926,13 +1926,13 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="34" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B49" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>8</v>
@@ -1976,13 +1976,13 @@
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="34" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B50" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>8</v>
@@ -1990,13 +1990,13 @@
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>8</v>
@@ -2004,13 +2004,13 @@
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B52" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>8</v>
@@ -2018,13 +2018,13 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B53" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>8</v>
@@ -2032,13 +2032,13 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>8</v>
@@ -2046,13 +2046,13 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>8</v>
@@ -2060,13 +2060,13 @@
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>8</v>
@@ -2074,13 +2074,13 @@
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>8</v>
@@ -2088,13 +2088,13 @@
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="34" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>8</v>
@@ -2102,13 +2102,13 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="34" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>8</v>
@@ -2116,13 +2116,13 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B60" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>8</v>
@@ -2130,13 +2130,13 @@
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B61" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C61" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>8</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>28</v>
@@ -2158,13 +2158,13 @@
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>28</v>
@@ -2172,13 +2172,13 @@
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>28</v>
@@ -2186,13 +2186,13 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>28</v>
@@ -2200,13 +2200,13 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>28</v>
@@ -2214,13 +2214,13 @@
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>28</v>
@@ -2228,13 +2228,13 @@
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>28</v>
@@ -2242,13 +2242,13 @@
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>28</v>
@@ -2256,13 +2256,13 @@
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>28</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -2278,13 +2278,13 @@
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>8</v>
@@ -2292,13 +2292,13 @@
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>8</v>
@@ -2306,13 +2306,13 @@
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>8</v>
@@ -2320,13 +2320,13 @@
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>8</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>8</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>8</v>
@@ -2362,13 +2362,13 @@
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>28</v>
@@ -2376,13 +2376,13 @@
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>28</v>
@@ -2390,13 +2390,13 @@
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>28</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>28</v>
@@ -2418,13 +2418,13 @@
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>28</v>
@@ -2432,13 +2432,13 @@
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>28</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -2454,13 +2454,13 @@
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C85" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>83</v>
       </c>
       <c r="D85" s="12" t="s">
         <v>8</v>
@@ -2468,13 +2468,13 @@
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>8</v>
@@ -2482,13 +2482,13 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D87" s="12" t="s">
         <v>8</v>
@@ -2496,13 +2496,13 @@
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>8</v>
@@ -2510,13 +2510,13 @@
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C89" s="11" t="s">
         <v>86</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>87</v>
       </c>
       <c r="D89" s="12" t="s">
         <v>28</v>
@@ -2524,13 +2524,13 @@
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>28</v>
@@ -2538,13 +2538,13 @@
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D91" s="12" t="s">
         <v>28</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>28</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>43</v>
@@ -2580,10 +2580,10 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>43</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C95" s="11" t="s">
         <v>43</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>43</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C97" s="13"/>
       <c r="D97" s="14" t="s">
@@ -2634,10 +2634,10 @@
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>43</v>
@@ -2648,7 +2648,7 @@
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>28</v>
@@ -2670,13 +2670,13 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>28</v>
@@ -2684,13 +2684,13 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>28</v>
@@ -2698,13 +2698,13 @@
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>28</v>
@@ -2712,13 +2712,13 @@
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D104" s="14" t="s">
         <v>28</v>
@@ -2726,13 +2726,13 @@
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D105" s="14" t="s">
         <v>28</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -2748,13 +2748,13 @@
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C107" s="15" t="s">
         <v>101</v>
-      </c>
-      <c r="B107" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C107" s="15" t="s">
-        <v>102</v>
       </c>
       <c r="D107" s="16" t="s">
         <v>28</v>
@@ -2762,13 +2762,13 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D108" s="16" t="s">
         <v>28</v>
@@ -2776,13 +2776,13 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D109" s="16" t="s">
         <v>28</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D110" s="16" t="s">
         <v>28</v>
@@ -2804,13 +2804,13 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C111" s="36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D111" s="37" t="s">
         <v>28</v>
@@ -2818,13 +2818,13 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D112" s="16" t="s">
         <v>28</v>
@@ -2832,13 +2832,13 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D113" s="16" t="s">
         <v>28</v>
@@ -2846,13 +2846,13 @@
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D114" s="16" t="s">
         <v>28</v>
@@ -2860,13 +2860,13 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D115" s="16" t="s">
         <v>28</v>
@@ -2874,13 +2874,13 @@
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D116" s="16" t="s">
         <v>28</v>
@@ -2888,13 +2888,13 @@
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D117" s="16" t="s">
         <v>28</v>
@@ -2902,13 +2902,13 @@
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D118" s="16" t="s">
         <v>28</v>
@@ -2916,13 +2916,13 @@
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D119" s="16" t="s">
         <v>28</v>
@@ -2930,13 +2930,13 @@
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D120" s="16" t="s">
         <v>28</v>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D121" s="16" t="s">
         <v>28</v>
@@ -2958,13 +2958,13 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D122" s="16" t="s">
         <v>28</v>
@@ -2972,13 +2972,13 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D123" s="16" t="s">
         <v>28</v>
@@ -2986,13 +2986,13 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D124" s="16" t="s">
         <v>28</v>
@@ -3000,13 +3000,13 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D125" s="16" t="s">
         <v>28</v>
@@ -3014,13 +3014,13 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D126" s="16" t="s">
         <v>28</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D127" s="16" t="s">
         <v>28</v>
@@ -3042,13 +3042,13 @@
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D128" s="16" t="s">
         <v>28</v>
@@ -3056,13 +3056,13 @@
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D129" s="16" t="s">
         <v>28</v>
@@ -3070,7 +3070,7 @@
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -3078,13 +3078,13 @@
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B131" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B131" s="17" t="s">
+      <c r="C131" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C131" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D131" s="18" t="s">
         <v>28</v>
@@ -3092,13 +3092,13 @@
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B132" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C132" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C132" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D132" s="18" t="s">
         <v>28</v>
@@ -3106,13 +3106,13 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B133" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C133" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C133" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D133" s="18" t="s">
         <v>28</v>
@@ -3120,13 +3120,13 @@
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B134" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C134" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C134" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D134" s="18" t="s">
         <v>28</v>
@@ -3134,13 +3134,13 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B135" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C135" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C135" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D135" s="18" t="s">
         <v>28</v>
@@ -3148,13 +3148,13 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B136" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C136" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C136" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D136" s="18" t="s">
         <v>28</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B137" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C137" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C137" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D137" s="18" t="s">
         <v>28</v>
@@ -3176,13 +3176,13 @@
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B138" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C138" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C138" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D138" s="18" t="s">
         <v>28</v>
@@ -3190,13 +3190,13 @@
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B139" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C139" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C139" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D139" s="18" t="s">
         <v>28</v>
@@ -3204,13 +3204,13 @@
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B140" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C140" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C140" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D140" s="18" t="s">
         <v>28</v>
@@ -3218,13 +3218,13 @@
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B141" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C141" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C141" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D141" s="18" t="s">
         <v>28</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B142" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C142" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C142" s="17" t="s">
-        <v>125</v>
       </c>
       <c r="D142" s="18" t="s">
         <v>28</v>
@@ -3246,13 +3246,13 @@
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B143" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C143" s="17" t="s">
         <v>137</v>
-      </c>
-      <c r="B143" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C143" s="17" t="s">
-        <v>138</v>
       </c>
       <c r="D143" s="18" t="s">
         <v>8</v>
@@ -3260,13 +3260,13 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D144" s="18" t="s">
         <v>8</v>
@@ -3274,13 +3274,13 @@
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D145" s="18" t="s">
         <v>8</v>
@@ -3288,13 +3288,13 @@
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D146" s="18" t="s">
         <v>8</v>
@@ -3302,7 +3302,7 @@
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -3310,13 +3310,13 @@
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B148" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D148" s="20" t="s">
         <v>28</v>
@@ -3324,13 +3324,13 @@
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B149" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D149" s="20" t="s">
         <v>28</v>
@@ -3338,13 +3338,13 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B150" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D150" s="20" t="s">
         <v>28</v>
@@ -3352,13 +3352,13 @@
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B151" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D151" s="20" t="s">
         <v>28</v>
@@ -3366,13 +3366,13 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B152" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C152" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D152" s="20" t="s">
         <v>28</v>
@@ -3380,13 +3380,13 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B153" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D153" s="20" t="s">
         <v>28</v>
@@ -3394,13 +3394,13 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B154" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C154" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D154" s="20" t="s">
         <v>28</v>
@@ -3408,13 +3408,13 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B155" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D155" s="20" t="s">
         <v>28</v>
@@ -3422,13 +3422,13 @@
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B156" s="38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C156" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D156" s="39" t="s">
         <v>28</v>
@@ -3436,7 +3436,7 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -3444,13 +3444,13 @@
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B158" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="B158" s="21" t="s">
+      <c r="C158" s="21" t="s">
         <v>152</v>
-      </c>
-      <c r="C158" s="21" t="s">
-        <v>153</v>
       </c>
       <c r="D158" s="22" t="s">
         <v>8</v>
@@ -3458,13 +3458,13 @@
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B159" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C159" s="21" t="s">
         <v>152</v>
-      </c>
-      <c r="C159" s="21" t="s">
-        <v>153</v>
       </c>
       <c r="D159" s="22" t="s">
         <v>8</v>
@@ -3472,13 +3472,13 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B160" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C160" s="21" t="s">
         <v>155</v>
-      </c>
-      <c r="B160" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="C160" s="21" t="s">
-        <v>156</v>
       </c>
       <c r="D160" s="22" t="s">
         <v>8</v>
@@ -3486,13 +3486,13 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C161" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D161" s="22" t="s">
         <v>8</v>
@@ -3500,13 +3500,13 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B162" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C162" s="21" t="s">
         <v>152</v>
-      </c>
-      <c r="C162" s="21" t="s">
-        <v>153</v>
       </c>
       <c r="D162" s="22" t="s">
         <v>8</v>
@@ -3514,13 +3514,13 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B163" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C163" s="21" t="s">
         <v>152</v>
-      </c>
-      <c r="C163" s="21" t="s">
-        <v>153</v>
       </c>
       <c r="D163" s="22" t="s">
         <v>8</v>
@@ -3528,13 +3528,13 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D164" s="22" t="s">
         <v>8</v>
@@ -3542,13 +3542,13 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>8</v>
@@ -3556,13 +3556,13 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D166" s="22" t="s">
         <v>8</v>
@@ -3570,13 +3570,13 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D167" s="22" t="s">
         <v>8</v>
@@ -3584,13 +3584,13 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D168" s="22" t="s">
         <v>8</v>
@@ -3598,13 +3598,13 @@
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B169" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D169" s="22" t="s">
         <v>8</v>
@@ -3612,13 +3612,13 @@
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="21" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B170" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D170" s="22" t="s">
         <v>8</v>
@@ -3626,13 +3626,13 @@
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B171" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C171" s="21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D171" s="22" t="s">
         <v>28</v>
@@ -3640,13 +3640,13 @@
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B172" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C172" s="21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D172" s="22" t="s">
         <v>28</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -3662,13 +3662,13 @@
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="B174" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="B174" s="23" t="s">
-        <v>165</v>
-      </c>
       <c r="C174" s="23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D174" s="24" t="s">
         <v>8</v>
@@ -3676,13 +3676,13 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B175" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C175" s="23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D175" s="24" t="s">
         <v>8</v>
@@ -3690,13 +3690,13 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B176" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D176" s="24" t="s">
         <v>8</v>
@@ -3704,13 +3704,13 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="B177" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C177" s="23" t="s">
         <v>168</v>
-      </c>
-      <c r="B177" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="C177" s="23" t="s">
-        <v>169</v>
       </c>
       <c r="D177" s="24" t="s">
         <v>8</v>
@@ -3718,13 +3718,13 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B178" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C178" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D178" s="24" t="s">
         <v>8</v>
@@ -3732,13 +3732,13 @@
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B179" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C179" s="23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D179" s="24" t="s">
         <v>8</v>
@@ -3746,13 +3746,13 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B180" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C180" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D180" s="24" t="s">
         <v>28</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B181" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C181" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D181" s="24" t="s">
         <v>28</v>
@@ -3774,13 +3774,13 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="23" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B182" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C182" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D182" s="24" t="s">
         <v>28</v>
@@ -3788,13 +3788,13 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B183" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C183" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D183" s="24" t="s">
         <v>28</v>
@@ -3802,13 +3802,13 @@
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B184" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C184" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D184" s="24" t="s">
         <v>28</v>
@@ -3816,13 +3816,13 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B185" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C185" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D185" s="24" t="s">
         <v>28</v>
@@ -3830,13 +3830,13 @@
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B186" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C186" s="23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D186" s="24" t="s">
         <v>28</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="B188" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C188" s="25" t="s">
         <v>178</v>
-      </c>
-      <c r="B188" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="C188" s="25" t="s">
-        <v>179</v>
       </c>
       <c r="D188" s="26" t="s">
         <v>8</v>
@@ -3866,13 +3866,13 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="B189" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C189" s="25" t="s">
         <v>180</v>
-      </c>
-      <c r="B189" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="C189" s="25" t="s">
-        <v>181</v>
       </c>
       <c r="D189" s="26" t="s">
         <v>8</v>
@@ -3880,13 +3880,13 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B190" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C190" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D190" s="26" t="s">
         <v>8</v>
@@ -3894,13 +3894,13 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B191" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D191" s="26" t="s">
         <v>8</v>
@@ -3908,13 +3908,13 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="25" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B192" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D192" s="26" t="s">
         <v>8</v>
@@ -3922,13 +3922,13 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B193" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C193" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D193" s="26" t="s">
         <v>28</v>
@@ -3936,13 +3936,13 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B194" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C194" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D194" s="26" t="s">
         <v>28</v>
@@ -3950,13 +3950,13 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B195" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C195" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D195" s="26" t="s">
         <v>28</v>
@@ -3964,13 +3964,13 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B196" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C196" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D196" s="26" t="s">
         <v>28</v>
@@ -3978,13 +3978,13 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B197" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C197" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D197" s="26" t="s">
         <v>28</v>
@@ -3992,7 +3992,7 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -4000,13 +4000,13 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B199" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C199" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D199" s="28" t="s">
         <v>28</v>
@@ -4014,13 +4014,13 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B200" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C200" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D200" s="28" t="s">
         <v>28</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B202" s="29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C202" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D202" s="30" t="s">
         <v>28</v>
@@ -4050,13 +4050,13 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B203" s="29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C203" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D203" s="30" t="s">
         <v>28</v>
@@ -4064,13 +4064,13 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="29" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B204" s="29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C204" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D204" s="30" t="s">
         <v>28</v>
@@ -4078,13 +4078,13 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="29" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B205" s="29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C205" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D205" s="30" t="s">
         <v>28</v>
@@ -4092,13 +4092,13 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B206" s="29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C206" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D206" s="30" t="s">
         <v>28</v>
@@ -4106,13 +4106,13 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B207" s="29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C207" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D207" s="30" t="s">
         <v>28</v>
@@ -4120,13 +4120,13 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B208" s="29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C208" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D208" s="30" t="s">
         <v>28</v>
@@ -4134,13 +4134,13 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B209" s="29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C209" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D209" s="30" t="s">
         <v>28</v>
@@ -4148,13 +4148,13 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B210" s="29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C210" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D210" s="30" t="s">
         <v>28</v>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -4170,13 +4170,13 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="B212" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="B212" s="31" t="s">
-        <v>201</v>
-      </c>
       <c r="C212" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D212" s="32" t="s">
         <v>28</v>
@@ -4184,13 +4184,13 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B213" s="31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C213" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D213" s="32" t="s">
         <v>28</v>
@@ -4198,13 +4198,13 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="31" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B214" s="31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C214" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D214" s="32" t="s">
         <v>28</v>
@@ -4212,13 +4212,13 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B215" s="31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C215" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D215" s="32" t="s">
         <v>28</v>

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F7A40C-1FAD-7244-8577-10FE1FBBC625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B63480-7B3E-394D-9321-F3896DB8A920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Übungsliste" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="252">
   <si>
     <t>Übung</t>
   </si>
@@ -120,12 +120,6 @@
     <t>Kabel Fliegende</t>
   </si>
   <si>
-    <t>LH Überzüge</t>
-  </si>
-  <si>
-    <t>Lat, Trizeps</t>
-  </si>
-  <si>
     <t>KH Überzüge</t>
   </si>
   <si>
@@ -141,9 +135,6 @@
     <t>Steck Dips (Brustbetont)</t>
   </si>
   <si>
-    <t>Kabel Dips (Brustbetont)</t>
-  </si>
-  <si>
     <t>■ LAT</t>
   </si>
   <si>
@@ -177,9 +168,6 @@
     <t>LH Überzüge, weit (Lat-betont)</t>
   </si>
   <si>
-    <t>Brust, Trizeps</t>
-  </si>
-  <si>
     <t>Kabel Überzüge, weit (Lat-betont)</t>
   </si>
   <si>
@@ -663,9 +651,6 @@
     <t>LH Rudern, schulterbreit, Obergriff</t>
   </si>
   <si>
-    <t>Multipresse Rudern, wschulterbreiteit, Obergriff</t>
-  </si>
-  <si>
     <t>Steck Rudern, schulterbreit, Obergriff</t>
   </si>
   <si>
@@ -786,10 +771,16 @@
     <t>Rudern Multipresse, Brustgestützt, Obergriff</t>
   </si>
   <si>
-    <t>KHRudern, Brustgestützt, Obergriff</t>
-  </si>
-  <si>
     <t>Latziehen zur Brust, Obergriff</t>
+  </si>
+  <si>
+    <t>KH Rudern, Brustgestützt, Obergriff</t>
+  </si>
+  <si>
+    <t>Multipresse Rudern, schulterbreiteit, Obergriff</t>
+  </si>
+  <si>
+    <t>Dips (Brustbetont)</t>
   </si>
 </sst>
 </file>
@@ -808,17 +799,20 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -964,7 +958,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1079,6 +1073,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1296,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D980"/>
+  <dimension ref="A1:D979"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
@@ -1343,50 +1343,50 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="B4" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="41" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>218</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>6</v>
@@ -1414,21 +1414,21 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>6</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>219</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>6</v>
@@ -1456,21 +1456,21 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>6</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>6</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>6</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>6</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>6</v>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>6</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>6</v>
@@ -1566,9 +1566,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
@@ -1582,7 +1582,7 @@
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>221</v>
+        <v>22</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>6</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>6</v>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>25</v>
+        <v>218</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>8</v>
@@ -1624,7 +1624,7 @@
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>26</v>
+        <v>214</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>6</v>
@@ -1633,12 +1633,12 @@
         <v>27</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>6</v>
@@ -1647,12 +1647,12 @@
         <v>27</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>29</v>
+        <v>217</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>6</v>
@@ -1666,91 +1666,91 @@
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>30</v>
+        <v>216</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>31</v>
+        <v>213</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>223</v>
+        <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>6</v>
@@ -1764,77 +1764,77 @@
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
+      <c r="A35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="D37" s="6" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="33" t="s">
-        <v>202</v>
+      <c r="A39" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>8</v>
@@ -1842,13 +1842,13 @@
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="33" t="s">
-        <v>254</v>
+        <v>198</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>8</v>
@@ -1856,13 +1856,13 @@
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="33" t="s">
-        <v>249</v>
+        <v>199</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>8</v>
@@ -1870,13 +1870,13 @@
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="33" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>8</v>
@@ -1884,41 +1884,41 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="5" t="s">
-        <v>46</v>
+      <c r="A44" s="33" t="s">
+        <v>245</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="5" t="s">
-        <v>48</v>
+      <c r="A45" s="33" t="s">
+        <v>246</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>8</v>
@@ -1926,119 +1926,119 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+    </row>
+    <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="C48" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="34" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="34" t="s">
-        <v>212</v>
+      <c r="A50" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="34" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C51" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="34" t="s">
-        <v>213</v>
-      </c>
       <c r="B52" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="34" t="s">
-        <v>208</v>
+        <v>60</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="7" t="s">
-        <v>204</v>
+      <c r="A54" s="34" t="s">
+        <v>207</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>8</v>
@@ -2046,13 +2046,13 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>8</v>
@@ -2060,27 +2060,27 @@
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>206</v>
+        <v>52</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="34" t="s">
-        <v>253</v>
+        <v>209</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>8</v>
@@ -2088,27 +2088,27 @@
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="34" t="s">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="34" t="s">
-        <v>215</v>
+      <c r="A59" s="7" t="s">
+        <v>201</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>8</v>
@@ -2116,13 +2116,13 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="34" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>8</v>
@@ -2130,55 +2130,55 @@
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>225</v>
+        <v>53</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="7" t="s">
-        <v>56</v>
+      <c r="A62" s="34" t="s">
+        <v>219</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>57</v>
+        <v>220</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>28</v>
@@ -2186,119 +2186,119 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="7" t="s">
-        <v>60</v>
+      <c r="A66" s="34" t="s">
+        <v>247</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="7" t="s">
-        <v>62</v>
+      <c r="A67" s="34" t="s">
+        <v>208</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>63</v>
+        <v>202</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>28</v>
-      </c>
+      <c r="A70" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
+      <c r="A71" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C72" s="35" t="s">
-        <v>72</v>
+      <c r="C72" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C73" s="35" t="s">
-        <v>72</v>
+      <c r="C73" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>8</v>
@@ -2306,13 +2306,13 @@
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>8</v>
@@ -2320,41 +2320,41 @@
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="s">
-        <v>226</v>
+        <v>72</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C75" s="35" t="s">
-        <v>72</v>
+      <c r="C75" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C76" s="35" t="s">
-        <v>72</v>
+      <c r="C76" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C77" s="9" t="s">
-        <v>72</v>
+      <c r="C77" s="35" t="s">
+        <v>68</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>8</v>
@@ -2362,13 +2362,13 @@
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>28</v>
@@ -2376,164 +2376,162 @@
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C79" s="9" t="s">
-        <v>74</v>
+      <c r="C79" s="35" t="s">
+        <v>68</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
-        <v>76</v>
+        <v>221</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C80" s="9" t="s">
-        <v>74</v>
+      <c r="C80" s="35" t="s">
+        <v>68</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C81" s="9" t="s">
-        <v>74</v>
+      <c r="C81" s="35" t="s">
+        <v>68</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>28</v>
-      </c>
+      <c r="A83" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
+      <c r="A84" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C85" s="11" t="s">
         <v>82</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>8</v>
+      <c r="A87" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C87" s="13"/>
+      <c r="D87" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>82</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="11" t="s">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2541,38 +2539,38 @@
         <v>87</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="11" t="s">
-        <v>89</v>
+        <v>222</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>8</v>
@@ -2580,27 +2578,27 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="11" t="s">
-        <v>90</v>
+        <v>223</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="11" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D95" s="12" t="s">
         <v>8</v>
@@ -2608,61 +2606,63 @@
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B97" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C97" s="13"/>
-      <c r="D97" s="14" t="s">
-        <v>28</v>
+      <c r="A97" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="11" t="s">
+      <c r="A98" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+    </row>
+    <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
+      <c r="B99" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="13" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>28</v>
@@ -2670,13 +2670,13 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="13" t="s">
-        <v>210</v>
+        <v>92</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>28</v>
@@ -2684,13 +2684,13 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="13" t="s">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>28</v>
@@ -2698,13 +2698,13 @@
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="13" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>28</v>
@@ -2712,49 +2712,49 @@
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+    </row>
+    <row r="106" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C106" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B104" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C104" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D104" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B105" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C105" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D105" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
+      <c r="D106" s="16" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D107" s="16" t="s">
         <v>28</v>
@@ -2762,13 +2762,13 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="15" t="s">
-        <v>207</v>
+        <v>115</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D108" s="16" t="s">
         <v>28</v>
@@ -2776,13 +2776,13 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="15" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D109" s="16" t="s">
         <v>28</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D110" s="16" t="s">
         <v>28</v>
@@ -2804,13 +2804,13 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="36" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C111" s="36" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D111" s="37" t="s">
         <v>28</v>
@@ -2818,13 +2818,13 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="15" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D112" s="16" t="s">
         <v>28</v>
@@ -2832,13 +2832,13 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D113" s="16" t="s">
         <v>28</v>
@@ -2846,13 +2846,13 @@
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="15" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D114" s="16" t="s">
         <v>28</v>
@@ -2860,13 +2860,13 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="15" t="s">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D115" s="16" t="s">
         <v>28</v>
@@ -2874,13 +2874,13 @@
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="15" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D116" s="16" t="s">
         <v>28</v>
@@ -2888,13 +2888,13 @@
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="15" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D117" s="16" t="s">
         <v>28</v>
@@ -2902,13 +2902,13 @@
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="15" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D118" s="16" t="s">
         <v>28</v>
@@ -2916,13 +2916,13 @@
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="15" t="s">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D119" s="16" t="s">
         <v>28</v>
@@ -2930,13 +2930,13 @@
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="15" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D120" s="16" t="s">
         <v>28</v>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D121" s="16" t="s">
         <v>28</v>
@@ -2958,13 +2958,13 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D122" s="16" t="s">
         <v>28</v>
@@ -2972,13 +2972,13 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="15" t="s">
-        <v>114</v>
+        <v>225</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D123" s="16" t="s">
         <v>28</v>
@@ -2986,13 +2986,13 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="15" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D124" s="16" t="s">
         <v>28</v>
@@ -3000,13 +3000,13 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="15" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D125" s="16" t="s">
         <v>28</v>
@@ -3014,13 +3014,13 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="15" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D126" s="16" t="s">
         <v>28</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="15" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D127" s="16" t="s">
         <v>28</v>
@@ -3042,63 +3042,63 @@
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B128" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C128" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D128" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+    </row>
+    <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B130" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="B128" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C128" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D128" s="16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B129" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C129" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D129" s="16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
+      <c r="C130" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="D130" s="18" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="17" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D131" s="18" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="17" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D132" s="18" t="s">
         <v>28</v>
@@ -3106,13 +3106,13 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="17" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C133" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D133" s="18" t="s">
         <v>28</v>
@@ -3120,13 +3120,13 @@
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="17" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D134" s="18" t="s">
         <v>28</v>
@@ -3134,13 +3134,13 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D135" s="18" t="s">
         <v>28</v>
@@ -3148,13 +3148,13 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="17" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D136" s="18" t="s">
         <v>28</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D137" s="18" t="s">
         <v>28</v>
@@ -3176,13 +3176,13 @@
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C138" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D138" s="18" t="s">
         <v>28</v>
@@ -3190,13 +3190,13 @@
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="17" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D139" s="18" t="s">
         <v>28</v>
@@ -3204,13 +3204,13 @@
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="17" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D140" s="18" t="s">
         <v>28</v>
@@ -3218,13 +3218,13 @@
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="17" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D141" s="18" t="s">
         <v>28</v>
@@ -3232,27 +3232,27 @@
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="17" t="s">
-        <v>135</v>
+        <v>226</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D142" s="18" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D143" s="18" t="s">
         <v>8</v>
@@ -3260,63 +3260,63 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="17" t="s">
-        <v>231</v>
+        <v>127</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D144" s="18" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="17" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D145" s="18" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="17" t="s">
+      <c r="A146" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+    </row>
+    <row r="147" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="B146" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="C146" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="D146" s="18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
+      <c r="B147" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D147" s="20" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B148" s="19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="D148" s="20" t="s">
         <v>28</v>
@@ -3327,10 +3327,10 @@
         <v>142</v>
       </c>
       <c r="B149" s="19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="D149" s="20" t="s">
         <v>28</v>
@@ -3338,41 +3338,41 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B150" s="19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="D150" s="20" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B151" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C151" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D151" s="20" t="s">
+      <c r="A151" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B151" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="C151" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D151" s="39" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="19" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B152" s="19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C152" s="19" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="D152" s="20" t="s">
         <v>28</v>
@@ -3380,13 +3380,13 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="19" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B153" s="19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D153" s="20" t="s">
         <v>28</v>
@@ -3394,13 +3394,13 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="19" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B154" s="19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C154" s="19" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D154" s="20" t="s">
         <v>28</v>
@@ -3408,49 +3408,49 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="19" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B155" s="19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="D155" s="20" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="B156" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="C156" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="D156" s="39" t="s">
-        <v>28</v>
-      </c>
+      <c r="A156" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B157" s="2"/>
-      <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
+      <c r="A157" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B157" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C157" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="D157" s="22" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="21" t="s">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D158" s="22" t="s">
         <v>8</v>
@@ -3458,13 +3458,13 @@
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="21" t="s">
-        <v>153</v>
+        <v>230</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C159" s="21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D159" s="22" t="s">
         <v>8</v>
@@ -3472,13 +3472,13 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B160" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C160" s="21" t="s">
         <v>154</v>
-      </c>
-      <c r="B160" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="C160" s="21" t="s">
-        <v>155</v>
       </c>
       <c r="D160" s="22" t="s">
         <v>8</v>
@@ -3486,13 +3486,13 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="21" t="s">
-        <v>156</v>
+        <v>231</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C161" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D161" s="22" t="s">
         <v>8</v>
@@ -3500,13 +3500,13 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="21" t="s">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="B162" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C162" s="21" t="s">
         <v>151</v>
-      </c>
-      <c r="C162" s="21" t="s">
-        <v>152</v>
       </c>
       <c r="D162" s="22" t="s">
         <v>8</v>
@@ -3514,13 +3514,13 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="21" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D163" s="22" t="s">
         <v>8</v>
@@ -3528,13 +3528,13 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="21" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D164" s="22" t="s">
         <v>8</v>
@@ -3542,13 +3542,13 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="21" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B165" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C165" s="21" t="s">
         <v>151</v>
-      </c>
-      <c r="C165" s="21" t="s">
-        <v>158</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>8</v>
@@ -3556,13 +3556,13 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="21" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D166" s="22" t="s">
         <v>8</v>
@@ -3570,13 +3570,13 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="21" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D167" s="22" t="s">
         <v>8</v>
@@ -3584,27 +3584,27 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="21" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="21" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B169" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D169" s="22" t="s">
         <v>8</v>
@@ -3612,13 +3612,13 @@
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="21" t="s">
-        <v>237</v>
+        <v>153</v>
       </c>
       <c r="B170" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D170" s="22" t="s">
         <v>8</v>
@@ -3626,49 +3626,49 @@
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="21" t="s">
-        <v>238</v>
+        <v>157</v>
       </c>
       <c r="B171" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C171" s="21" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D171" s="22" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="B172" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="C172" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D172" s="22" t="s">
-        <v>28</v>
-      </c>
+      <c r="A172" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B173" s="2"/>
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
+      <c r="A173" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="B173" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C173" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D173" s="24" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B174" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C174" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D174" s="24" t="s">
         <v>8</v>
@@ -3676,13 +3676,13 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="23" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B175" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C175" s="23" t="s">
         <v>164</v>
-      </c>
-      <c r="C175" s="23" t="s">
-        <v>155</v>
       </c>
       <c r="D175" s="24" t="s">
         <v>8</v>
@@ -3693,10 +3693,10 @@
         <v>166</v>
       </c>
       <c r="B176" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D176" s="24" t="s">
         <v>8</v>
@@ -3704,13 +3704,13 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="23" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B177" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C177" s="23" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="D177" s="24" t="s">
         <v>8</v>
@@ -3718,13 +3718,13 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="23" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B178" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C178" s="23" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="D178" s="24" t="s">
         <v>8</v>
@@ -3732,27 +3732,27 @@
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B179" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C179" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D179" s="24" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="23" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B180" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C180" s="23" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D180" s="24" t="s">
         <v>28</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="23" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="B181" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C181" s="23" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D181" s="24" t="s">
         <v>28</v>
@@ -3774,13 +3774,13 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="23" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B182" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C182" s="23" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D182" s="24" t="s">
         <v>28</v>
@@ -3788,13 +3788,13 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="23" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B183" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C183" s="23" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D183" s="24" t="s">
         <v>28</v>
@@ -3802,13 +3802,13 @@
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="23" t="s">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="B184" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C184" s="23" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D184" s="24" t="s">
         <v>28</v>
@@ -3816,77 +3816,77 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="23" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B185" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C185" s="23" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D185" s="24" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="B186" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="C186" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="D186" s="24" t="s">
-        <v>28</v>
-      </c>
+      <c r="A186" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B187" s="2"/>
-      <c r="C187" s="2"/>
-      <c r="D187" s="2"/>
+      <c r="A187" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="B187" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="C187" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="D187" s="26" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="25" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B188" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C188" s="25" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="D188" s="26" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="25" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B189" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C189" s="25" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D189" s="26" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="25" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B190" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C190" s="25" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D190" s="26" t="s">
         <v>8</v>
@@ -3894,13 +3894,13 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="25" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B191" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D191" s="26" t="s">
         <v>8</v>
@@ -3908,13 +3908,13 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="25" t="s">
-        <v>242</v>
+        <v>175</v>
       </c>
       <c r="B192" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D192" s="26" t="s">
         <v>8</v>
@@ -3922,27 +3922,27 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="25" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B193" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C193" s="25" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D193" s="26" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="25" t="s">
-        <v>184</v>
+        <v>238</v>
       </c>
       <c r="B194" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="C194" s="25" t="s">
-        <v>164</v>
+        <v>151</v>
+      </c>
+      <c r="C194" s="27" t="s">
+        <v>120</v>
       </c>
       <c r="D194" s="26" t="s">
         <v>28</v>
@@ -3950,99 +3950,99 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="25" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="B195" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C195" s="25" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D195" s="26" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="25" t="s">
-        <v>243</v>
+        <v>182</v>
       </c>
       <c r="B196" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="C196" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+      <c r="C196" s="27" t="s">
+        <v>120</v>
       </c>
       <c r="D196" s="26" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="B197" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="C197" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="D197" s="26" t="s">
-        <v>28</v>
-      </c>
+      <c r="A197" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
+      <c r="A198" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="B198" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="C198" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D198" s="28" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="27" t="s">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="B199" s="27" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C199" s="27" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D199" s="28" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="27" t="s">
+      <c r="A200" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+    </row>
+    <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="B200" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="C200" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="D200" s="28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B201" s="2"/>
-      <c r="C201" s="2"/>
-      <c r="D201" s="2"/>
+      <c r="B201" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C201" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="D201" s="30" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="29" t="s">
         <v>191</v>
       </c>
       <c r="B202" s="29" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C202" s="29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D202" s="30" t="s">
         <v>28</v>
@@ -4050,13 +4050,13 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="29" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B203" s="29" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C203" s="29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D203" s="30" t="s">
         <v>28</v>
@@ -4064,13 +4064,13 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B204" s="29" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C204" s="29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D204" s="30" t="s">
         <v>28</v>
@@ -4078,13 +4078,13 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="29" t="s">
-        <v>245</v>
+        <v>188</v>
       </c>
       <c r="B205" s="29" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C205" s="29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D205" s="30" t="s">
         <v>28</v>
@@ -4092,13 +4092,13 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="29" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="B206" s="29" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C206" s="29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D206" s="30" t="s">
         <v>28</v>
@@ -4106,13 +4106,13 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="29" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="B207" s="29" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C207" s="29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D207" s="30" t="s">
         <v>28</v>
@@ -4120,13 +4120,13 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B208" s="29" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C208" s="29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D208" s="30" t="s">
         <v>28</v>
@@ -4134,49 +4134,49 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="29" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="B209" s="29" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C209" s="29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D209" s="30" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="29" t="s">
+      <c r="A210" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B210" s="2"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
+    </row>
+    <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="B210" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="C210" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="D210" s="30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B211" s="2"/>
-      <c r="C211" s="2"/>
-      <c r="D211" s="2"/>
+      <c r="B211" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="C211" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D211" s="32" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="31" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B212" s="31" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C212" s="31" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D212" s="32" t="s">
         <v>28</v>
@@ -4184,13 +4184,13 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="31" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="B213" s="31" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C213" s="31" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D213" s="32" t="s">
         <v>28</v>
@@ -4198,32 +4198,19 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="31" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B214" s="31" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C214" s="31" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D214" s="32" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="B215" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="C215" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="D215" s="32" t="s">
-        <v>28</v>
-      </c>
-    </row>
+    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4988,8 +4975,10 @@
     <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A211:D214">
+    <sortCondition ref="A211:A214"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B63480-7B3E-394D-9321-F3896DB8A920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85008493-AFE4-FC43-B4CC-B8F6C1C98C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="253">
   <si>
     <t>Übung</t>
   </si>
@@ -612,9 +612,6 @@
     <t>■ ABS</t>
   </si>
   <si>
-    <t>Kabel Crunches (Varianten)</t>
-  </si>
-  <si>
     <t>Abs</t>
   </si>
   <si>
@@ -711,21 +708,6 @@
     <t>PlateLoaded Beinpresse</t>
   </si>
   <si>
-    <t>PlateLoaded Hackenschmidt-Kniebeugen</t>
-  </si>
-  <si>
-    <t>LH SPlateLoadeditsquats</t>
-  </si>
-  <si>
-    <t>KH SPlateLoadeditsquats</t>
-  </si>
-  <si>
-    <t>LH Bulgarian SPlateLoadeditsquats</t>
-  </si>
-  <si>
-    <t>KH Bulgarian SPlateLoadeditsquats</t>
-  </si>
-  <si>
     <t>PlateLoaded Beinstrecken</t>
   </si>
   <si>
@@ -753,12 +735,6 @@
     <t>PlateLoaded Wadenheben, sitzend</t>
   </si>
   <si>
-    <t>PlateLoadedanks</t>
-  </si>
-  <si>
-    <t>SidePlateLoadedanks</t>
-  </si>
-  <si>
     <t>Latziehen in den Nacken, Obergriff, weit</t>
   </si>
   <si>
@@ -781,6 +757,33 @@
   </si>
   <si>
     <t>Dips (Brustbetont)</t>
+  </si>
+  <si>
+    <t>KH Bulgarian Splitsquats</t>
+  </si>
+  <si>
+    <t>LH Bulgarian Splitsquats</t>
+  </si>
+  <si>
+    <t>PlateLoaded Hackenschmidt</t>
+  </si>
+  <si>
+    <t>Planks</t>
+  </si>
+  <si>
+    <t>Sideplanks</t>
+  </si>
+  <si>
+    <t>Kabel Crunches</t>
+  </si>
+  <si>
+    <t>LH/KH Heben Fatgripz</t>
+  </si>
+  <si>
+    <t>Scheiben Heben</t>
+  </si>
+  <si>
+    <t>Deadhang</t>
   </si>
 </sst>
 </file>
@@ -1296,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D979"/>
+  <dimension ref="A1:D980"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1344,7 +1347,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="40" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B4" s="40" t="s">
         <v>6</v>
@@ -1610,7 +1613,7 @@
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>6</v>
@@ -1624,7 +1627,7 @@
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>6</v>
@@ -1638,7 +1641,7 @@
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>6</v>
@@ -1652,7 +1655,7 @@
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>6</v>
@@ -1666,7 +1669,7 @@
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
@@ -1680,7 +1683,7 @@
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>6</v>
@@ -1842,7 +1845,7 @@
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="33" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>37</v>
@@ -1856,7 +1859,7 @@
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>37</v>
@@ -1870,7 +1873,7 @@
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="33" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>37</v>
@@ -1884,7 +1887,7 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="33" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>37</v>
@@ -1898,7 +1901,7 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="33" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>37</v>
@@ -1912,7 +1915,7 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="33" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>37</v>
@@ -1962,7 +1965,7 @@
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="34" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>49</v>
@@ -1990,7 +1993,7 @@
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="34" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>49</v>
@@ -2032,7 +2035,7 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>49</v>
@@ -2046,7 +2049,7 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>49</v>
@@ -2074,7 +2077,7 @@
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>49</v>
@@ -2088,7 +2091,7 @@
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>49</v>
@@ -2102,7 +2105,7 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>49</v>
@@ -2116,7 +2119,7 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="34" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>49</v>
@@ -2144,7 +2147,7 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>49</v>
@@ -2158,7 +2161,7 @@
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>49</v>
@@ -2200,7 +2203,7 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="34" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>49</v>
@@ -2214,7 +2217,7 @@
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>49</v>
@@ -2228,7 +2231,7 @@
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>49</v>
@@ -2390,7 +2393,7 @@
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>27</v>
@@ -2564,7 +2567,7 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>70</v>
@@ -2578,7 +2581,7 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>70</v>
@@ -2656,7 +2659,7 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B100" s="13" t="s">
         <v>57</v>
@@ -2684,7 +2687,7 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B102" s="13" t="s">
         <v>57</v>
@@ -2698,7 +2701,7 @@
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B103" s="13" t="s">
         <v>57</v>
@@ -2804,7 +2807,7 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B111" s="36" t="s">
         <v>42</v>
@@ -2860,7 +2863,7 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B115" s="15" t="s">
         <v>42</v>
@@ -2972,7 +2975,7 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B123" s="15" t="s">
         <v>42</v>
@@ -3232,7 +3235,7 @@
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B142" s="17" t="s">
         <v>119</v>
@@ -3294,15 +3297,15 @@
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
     </row>
-    <row r="147" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="19" t="s">
-        <v>139</v>
+        <v>252</v>
       </c>
       <c r="B147" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="D147" s="20" t="s">
         <v>28</v>
@@ -3310,13 +3313,13 @@
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="19" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B148" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="D148" s="20" t="s">
         <v>28</v>
@@ -3324,7 +3327,7 @@
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B149" s="19" t="s">
         <v>97</v>
@@ -3338,7 +3341,7 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B150" s="19" t="s">
         <v>97</v>
@@ -3350,43 +3353,43 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="B151" s="38" t="s">
+    <row r="151" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B151" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C151" s="38" t="s">
+      <c r="C151" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D151" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="B152" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="C152" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="D151" s="39" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="B152" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C152" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D152" s="20" t="s">
+      <c r="D152" s="39" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="19" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B153" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="D153" s="20" t="s">
         <v>28</v>
@@ -3394,7 +3397,7 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B154" s="19" t="s">
         <v>97</v>
@@ -3408,71 +3411,69 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B155" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C155" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D155" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="B156" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C156" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D156" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="B157" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C157" s="19"/>
+      <c r="D157" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B158" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C158" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D155" s="20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="2" t="s">
+      <c r="D158" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B156" s="2"/>
-      <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
-    </row>
-    <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="B157" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="C157" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D157" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="B158" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="C158" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D158" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="B159" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="C159" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D159" s="22" t="s">
-        <v>8</v>
-      </c>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B160" s="21" t="s">
         <v>147</v>
@@ -3486,7 +3487,7 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="21" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B161" s="21" t="s">
         <v>147</v>
@@ -3500,13 +3501,13 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="21" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B162" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D162" s="22" t="s">
         <v>8</v>
@@ -3514,13 +3515,13 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="21" t="s">
-        <v>146</v>
+        <v>245</v>
       </c>
       <c r="B163" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D163" s="22" t="s">
         <v>8</v>
@@ -3528,13 +3529,13 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="21" t="s">
-        <v>229</v>
+        <v>150</v>
       </c>
       <c r="B164" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D164" s="22" t="s">
         <v>8</v>
@@ -3542,13 +3543,13 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="21" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B165" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>8</v>
@@ -3556,13 +3557,13 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="21" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B166" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D166" s="22" t="s">
         <v>8</v>
@@ -3570,7 +3571,7 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="21" t="s">
-        <v>227</v>
+        <v>149</v>
       </c>
       <c r="B167" s="21" t="s">
         <v>147</v>
@@ -3584,41 +3585,41 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="21" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B168" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B169" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="D169" s="22" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="21" t="s">
-        <v>153</v>
+        <v>246</v>
       </c>
       <c r="B170" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D170" s="22" t="s">
         <v>8</v>
@@ -3626,49 +3627,49 @@
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="21" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B171" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C171" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D171" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B172" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C172" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="D171" s="22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="2" t="s">
+      <c r="D172" s="22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B172" s="2"/>
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
-    </row>
-    <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="B173" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="C173" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="D173" s="24" t="s">
-        <v>8</v>
-      </c>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="23" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B174" s="23" t="s">
         <v>160</v>
       </c>
       <c r="C174" s="23" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D174" s="24" t="s">
         <v>8</v>
@@ -3676,13 +3677,13 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B175" s="23" t="s">
         <v>160</v>
       </c>
       <c r="C175" s="23" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D175" s="24" t="s">
         <v>8</v>
@@ -3690,13 +3691,13 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="23" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B176" s="23" t="s">
         <v>160</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D176" s="24" t="s">
         <v>8</v>
@@ -3704,7 +3705,7 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="23" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B177" s="23" t="s">
         <v>160</v>
@@ -3718,7 +3719,7 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="23" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B178" s="23" t="s">
         <v>160</v>
@@ -3732,7 +3733,7 @@
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="23" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="B179" s="23" t="s">
         <v>160</v>
@@ -3741,18 +3742,18 @@
         <v>151</v>
       </c>
       <c r="D179" s="24" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="23" t="s">
-        <v>234</v>
+        <v>171</v>
       </c>
       <c r="B180" s="23" t="s">
         <v>160</v>
       </c>
       <c r="C180" s="23" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="D180" s="24" t="s">
         <v>28</v>
@@ -3760,7 +3761,7 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="23" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B181" s="23" t="s">
         <v>160</v>
@@ -3774,7 +3775,7 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="23" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B182" s="23" t="s">
         <v>160</v>
@@ -3788,7 +3789,7 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="23" t="s">
-        <v>168</v>
+        <v>229</v>
       </c>
       <c r="B183" s="23" t="s">
         <v>160</v>
@@ -3802,7 +3803,7 @@
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="23" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B184" s="23" t="s">
         <v>160</v>
@@ -3816,7 +3817,7 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B185" s="23" t="s">
         <v>160</v>
@@ -3829,30 +3830,30 @@
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="2" t="s">
+      <c r="A186" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B186" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C186" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="D186" s="24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B186" s="2"/>
-      <c r="C186" s="2"/>
-      <c r="D186" s="2"/>
-    </row>
-    <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="B187" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C187" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="D187" s="26" t="s">
-        <v>28</v>
-      </c>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="25" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B188" s="25" t="s">
         <v>151</v>
@@ -3866,7 +3867,7 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B189" s="25" t="s">
         <v>151</v>
@@ -3880,7 +3881,7 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B190" s="25" t="s">
         <v>151</v>
@@ -3889,18 +3890,18 @@
         <v>160</v>
       </c>
       <c r="D190" s="26" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="25" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B191" s="25" t="s">
         <v>151</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D191" s="26" t="s">
         <v>8</v>
@@ -3908,13 +3909,13 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B192" s="25" t="s">
         <v>151</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D192" s="26" t="s">
         <v>8</v>
@@ -3922,13 +3923,13 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="25" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B193" s="25" t="s">
         <v>151</v>
       </c>
       <c r="C193" s="25" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D193" s="26" t="s">
         <v>8</v>
@@ -3936,71 +3937,71 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="25" t="s">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="B194" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="C194" s="27" t="s">
-        <v>120</v>
+      <c r="C194" s="25" t="s">
+        <v>160</v>
       </c>
       <c r="D194" s="26" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="25" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B195" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="C195" s="25" t="s">
-        <v>160</v>
+      <c r="C195" s="27" t="s">
+        <v>120</v>
       </c>
       <c r="D195" s="26" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="25" t="s">
-        <v>182</v>
+        <v>231</v>
       </c>
       <c r="B196" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="C196" s="27" t="s">
+      <c r="C196" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="D196" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="B197" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="C197" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="D196" s="26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="2" t="s">
+      <c r="D197" s="26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B197" s="2"/>
-      <c r="C197" s="2"/>
-      <c r="D197" s="2"/>
-    </row>
-    <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="B198" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="C198" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D198" s="28" t="s">
-        <v>28</v>
-      </c>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="27" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="B199" s="27" t="s">
         <v>184</v>
@@ -4013,30 +4014,30 @@
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="2" t="s">
+      <c r="A200" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="B200" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="C200" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D200" s="28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B200" s="2"/>
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
-    </row>
-    <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="B201" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="C201" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="D201" s="30" t="s">
-        <v>28</v>
-      </c>
+      <c r="B201" s="2"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B202" s="29" t="s">
         <v>167</v>
@@ -4050,7 +4051,7 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="29" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B203" s="29" t="s">
         <v>167</v>
@@ -4064,7 +4065,7 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="29" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B204" s="29" t="s">
         <v>167</v>
@@ -4078,7 +4079,7 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="29" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B205" s="29" t="s">
         <v>167</v>
@@ -4092,7 +4093,7 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="29" t="s">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="B206" s="29" t="s">
         <v>167</v>
@@ -4106,7 +4107,7 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="29" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B207" s="29" t="s">
         <v>167</v>
@@ -4120,7 +4121,7 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="29" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="B208" s="29" t="s">
         <v>167</v>
@@ -4134,7 +4135,7 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="29" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B209" s="29" t="s">
         <v>167</v>
@@ -4147,33 +4148,33 @@
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="2" t="s">
+      <c r="A210" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="B210" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C210" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="D210" s="30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B210" s="2"/>
-      <c r="C210" s="2"/>
-      <c r="D210" s="2"/>
-    </row>
-    <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="B211" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="C211" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D211" s="32" t="s">
-        <v>28</v>
-      </c>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B212" s="31" t="s">
         <v>195</v>
-      </c>
-      <c r="B212" s="31" t="s">
-        <v>196</v>
       </c>
       <c r="C212" s="31" t="s">
         <v>120</v>
@@ -4184,10 +4185,10 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="31" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B213" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C213" s="31" t="s">
         <v>120</v>
@@ -4198,10 +4199,10 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="31" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B214" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C214" s="31" t="s">
         <v>120</v>
@@ -4210,7 +4211,20 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="B215" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="C215" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D215" s="32" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4975,9 +4989,10 @@
     <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A211:D214">
-    <sortCondition ref="A211:A214"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A212:D215">
+    <sortCondition ref="A212:A215"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D633F95-96A0-234B-8BD7-E86941C818FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA27691-C726-0C47-8ED5-DDAE3C2F7C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="14420" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="274">
   <si>
     <t>Übung</t>
   </si>
@@ -388,15 +388,9 @@
     <t>Kabel Reverse Flys</t>
   </si>
   <si>
-    <t>Kabel Seitheben, vorgebeugt, Obergriff</t>
-  </si>
-  <si>
     <t>KH Reverse Flys</t>
   </si>
   <si>
-    <t>KH Seitheben, vorgebeugt, Obergriff</t>
-  </si>
-  <si>
     <t>PlateLoaded Reverse Flys</t>
   </si>
   <si>
@@ -499,9 +493,6 @@
     <t>—</t>
   </si>
   <si>
-    <t>Kabel Trizepsstrecken, einarmig</t>
-  </si>
-  <si>
     <t>Kabel Trizepsstrecken, Obergriff</t>
   </si>
   <si>
@@ -688,12 +679,6 @@
     <t>Kabel Kickbacks</t>
   </si>
   <si>
-    <t>KH Back Extensions, horizontal</t>
-  </si>
-  <si>
-    <t>LH Back Extensions, horizontal</t>
-  </si>
-  <si>
     <t>LH Hip Thrust</t>
   </si>
   <si>
@@ -800,6 +785,63 @@
   </si>
   <si>
     <t>Kabel Abduktionen</t>
+  </si>
+  <si>
+    <t>Kabel Seitheben, vorgebeugt</t>
+  </si>
+  <si>
+    <t>KH Seitheben, vorgebeugt</t>
+  </si>
+  <si>
+    <t>Rear Delt Rows</t>
+  </si>
+  <si>
+    <t>Donkeywadenheben</t>
+  </si>
+  <si>
+    <t>Pendulum Squats</t>
+  </si>
+  <si>
+    <t>Multipresse Ausfallschritte</t>
+  </si>
+  <si>
+    <t>KH/Kettlebell Goblet Squats</t>
+  </si>
+  <si>
+    <t>KH StepUps</t>
+  </si>
+  <si>
+    <t>LH StepUps</t>
+  </si>
+  <si>
+    <t>Belt Squats</t>
+  </si>
+  <si>
+    <t>Kabel Pull-Througs</t>
+  </si>
+  <si>
+    <t>SZ JM Press</t>
+  </si>
+  <si>
+    <t>Kabel Trizepsstrecken, neutral</t>
+  </si>
+  <si>
+    <t>LH Seal Rows</t>
+  </si>
+  <si>
+    <t>Plate Loaded High Rows</t>
+  </si>
+  <si>
+    <t>Plate Loaded Low Rows</t>
+  </si>
+  <si>
+    <t>Glute Ham Raises</t>
+  </si>
+  <si>
+    <t>KH Back Extensions</t>
+  </si>
+  <si>
+    <t>LH Back Extensions</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D987"/>
+  <dimension ref="A1:D1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1924,105 +1966,105 @@
     </row>
     <row r="46" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>60</v>
+        <v>269</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C46" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
+      <c r="D47" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-    </row>
-    <row r="48" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="7" t="s">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="34" t="s">
-        <v>65</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="7" t="s">
-        <v>67</v>
+      <c r="A50" s="34" t="s">
+        <v>65</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="34" t="s">
-        <v>68</v>
+      <c r="A51" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="7" t="s">
-        <v>70</v>
+      <c r="A52" s="34" t="s">
+        <v>68</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="34" t="s">
-        <v>71</v>
+      <c r="A53" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>12</v>
@@ -2030,27 +2072,27 @@
     </row>
     <row r="54" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="7" t="s">
-        <v>73</v>
+      <c r="A55" s="34" t="s">
+        <v>72</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>8</v>
@@ -2058,35 +2100,35 @@
     </row>
     <row r="56" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="34" t="s">
-        <v>75</v>
+      <c r="A57" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>63</v>
@@ -2099,22 +2141,22 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="7" t="s">
-        <v>77</v>
+      <c r="A59" s="34" t="s">
+        <v>76</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="34" t="s">
-        <v>78</v>
+      <c r="A60" s="7" t="s">
+        <v>268</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>63</v>
@@ -2128,21 +2170,21 @@
     </row>
     <row r="61" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>63</v>
@@ -2156,169 +2198,169 @@
     </row>
     <row r="63" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="7" t="s">
-        <v>82</v>
+      <c r="A64" s="34" t="s">
+        <v>80</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="34" t="s">
-        <v>84</v>
+      <c r="A66" s="7" t="s">
+        <v>270</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="34" t="s">
-        <v>85</v>
+      <c r="A67" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="7" t="s">
-        <v>87</v>
+      <c r="A69" s="34" t="s">
+        <v>84</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C69" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D69" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
+      <c r="D72" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-    </row>
-    <row r="71" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>8</v>
-      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
     </row>
     <row r="74" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C74" s="35" t="s">
-        <v>93</v>
+      <c r="C74" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>11</v>
@@ -2332,21 +2374,21 @@
     </row>
     <row r="76" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>11</v>
@@ -2360,7 +2402,7 @@
     </row>
     <row r="78" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>11</v>
@@ -2374,21 +2416,21 @@
     </row>
     <row r="79" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C79" s="35" t="s">
-        <v>93</v>
+      <c r="C79" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>11</v>
@@ -2402,97 +2444,99 @@
     </row>
     <row r="81" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C81" s="35" t="s">
-        <v>93</v>
+      <c r="C81" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="C82" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D82" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="2" t="s">
+      <c r="D85" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-    </row>
-    <row r="84" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="11" t="s">
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+    </row>
+    <row r="87" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B87" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C87" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D84" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C87" s="13"/>
-      <c r="D87" s="14" t="s">
-        <v>12</v>
+      <c r="D87" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>90</v>
@@ -2506,7 +2550,7 @@
     </row>
     <row r="89" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>90</v>
@@ -2519,42 +2563,40 @@
       </c>
     </row>
     <row r="90" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B90" s="11" t="s">
+      <c r="A90" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B90" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C90" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>8</v>
+      <c r="C90" s="13"/>
+      <c r="D90" s="14" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>8</v>
@@ -2562,7 +2604,7 @@
     </row>
     <row r="93" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>90</v>
@@ -2576,21 +2618,21 @@
     </row>
     <row r="94" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>90</v>
@@ -2604,85 +2646,85 @@
     </row>
     <row r="96" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C97" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C100" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D97" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="2" t="s">
+      <c r="D100" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-    </row>
-    <row r="99" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B99" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C99" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D99" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B100" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C100" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B101" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C101" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D101" s="14" t="s">
-        <v>12</v>
-      </c>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
     </row>
     <row r="102" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B102" s="13" t="s">
         <v>64</v>
@@ -2696,7 +2738,7 @@
     </row>
     <row r="103" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="13" t="s">
-        <v>125</v>
+        <v>255</v>
       </c>
       <c r="B103" s="13" t="s">
         <v>64</v>
@@ -2710,7 +2752,7 @@
     </row>
     <row r="104" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B104" s="13" t="s">
         <v>64</v>
@@ -2723,106 +2765,106 @@
       </c>
     </row>
     <row r="105" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
+      <c r="A105" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="106" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B106" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C106" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D106" s="16" t="s">
+      <c r="A106" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D106" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B107" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C107" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D107" s="16" t="s">
+      <c r="A107" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B107" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D107" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B108" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C108" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D108" s="16" t="s">
+      <c r="A108" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D108" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B109" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C109" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D109" s="16" t="s">
-        <v>12</v>
-      </c>
+      <c r="A109" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
     </row>
     <row r="110" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="15" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B110" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D110" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="B111" s="36" t="s">
+      <c r="A111" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B111" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C111" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="D111" s="37" t="s">
+      <c r="C111" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D111" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="15" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B112" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D112" s="16" t="s">
         <v>12</v>
@@ -2830,13 +2872,13 @@
     </row>
     <row r="113" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B113" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D113" s="16" t="s">
         <v>12</v>
@@ -2844,41 +2886,41 @@
     </row>
     <row r="114" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B114" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D114" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B115" s="15" t="s">
+      <c r="A115" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B115" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="C115" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D115" s="16" t="s">
+      <c r="C115" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="D115" s="37" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="15" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B116" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D116" s="16" t="s">
         <v>12</v>
@@ -2886,13 +2928,13 @@
     </row>
     <row r="117" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="15" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B117" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D117" s="16" t="s">
         <v>12</v>
@@ -2900,13 +2942,13 @@
     </row>
     <row r="118" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="15" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B118" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D118" s="16" t="s">
         <v>12</v>
@@ -2914,13 +2956,13 @@
     </row>
     <row r="119" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="15" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B119" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D119" s="16" t="s">
         <v>12</v>
@@ -2928,13 +2970,13 @@
     </row>
     <row r="120" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="15" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B120" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D120" s="16" t="s">
         <v>12</v>
@@ -2942,13 +2984,13 @@
     </row>
     <row r="121" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="15" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B121" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D121" s="16" t="s">
         <v>12</v>
@@ -2956,13 +2998,13 @@
     </row>
     <row r="122" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B122" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D122" s="16" t="s">
         <v>12</v>
@@ -2970,13 +3012,13 @@
     </row>
     <row r="123" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="15" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B123" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D123" s="16" t="s">
         <v>12</v>
@@ -2984,13 +3026,13 @@
     </row>
     <row r="124" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="15" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B124" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D124" s="16" t="s">
         <v>12</v>
@@ -2998,13 +3040,13 @@
     </row>
     <row r="125" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="15" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B125" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D125" s="16" t="s">
         <v>12</v>
@@ -3012,13 +3054,13 @@
     </row>
     <row r="126" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="15" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B126" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D126" s="16" t="s">
         <v>12</v>
@@ -3026,13 +3068,13 @@
     </row>
     <row r="127" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="15" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B127" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D127" s="16" t="s">
         <v>12</v>
@@ -3040,119 +3082,119 @@
     </row>
     <row r="128" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="15" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B128" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D128" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
+      <c r="A129" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B129" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C129" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D129" s="16" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="130" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="B130" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C130" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="D130" s="18" t="s">
-        <v>8</v>
+      <c r="A130" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B130" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C130" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D130" s="16" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="B131" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C131" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="D131" s="18" t="s">
-        <v>8</v>
+      <c r="A131" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B131" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C131" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D131" s="16" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B132" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C132" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D132" s="18" t="s">
+      <c r="A132" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B132" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C132" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D132" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B133" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C133" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D133" s="18" t="s">
-        <v>12</v>
-      </c>
+      <c r="A133" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
     </row>
     <row r="134" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="17" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D134" s="18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="17" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D136" s="18" t="s">
         <v>12</v>
@@ -3160,13 +3202,13 @@
     </row>
     <row r="137" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="17" t="s">
-        <v>163</v>
+        <v>267</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D137" s="18" t="s">
         <v>12</v>
@@ -3174,13 +3216,13 @@
     </row>
     <row r="138" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="17" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C138" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D138" s="18" t="s">
         <v>12</v>
@@ -3188,13 +3230,13 @@
     </row>
     <row r="139" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="17" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D139" s="18" t="s">
         <v>12</v>
@@ -3202,13 +3244,13 @@
     </row>
     <row r="140" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="17" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D140" s="18" t="s">
         <v>12</v>
@@ -3216,13 +3258,13 @@
     </row>
     <row r="141" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="17" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D141" s="18" t="s">
         <v>12</v>
@@ -3230,41 +3272,41 @@
     </row>
     <row r="142" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="17" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D142" s="18" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="17" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D143" s="18" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="17" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D144" s="18" t="s">
         <v>12</v>
@@ -3272,116 +3314,116 @@
     </row>
     <row r="145" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="17" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D145" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-    </row>
-    <row r="147" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="B147" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C147" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="D147" s="20" t="s">
-        <v>12</v>
+      <c r="A146" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B146" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C146" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="D146" s="18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B147" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C147" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="D147" s="18" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B148" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C148" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D148" s="20" t="s">
+      <c r="A148" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B148" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C148" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="D148" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="B149" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C149" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="D149" s="20" t="s">
+      <c r="A149" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B149" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C149" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="D149" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B150" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C150" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="D150" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="B151" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C151" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="D151" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="B152" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="C152" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D152" s="39" t="s">
+      <c r="A150" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B150" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C150" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="D150" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+    </row>
+    <row r="152" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C152" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="D152" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="19" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B153" s="19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C153" s="19" t="s">
         <v>58</v>
@@ -3392,13 +3434,13 @@
     </row>
     <row r="154" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="19" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B154" s="19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C154" s="19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D154" s="20" t="s">
         <v>12</v>
@@ -3406,50 +3448,52 @@
     </row>
     <row r="155" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="19" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B155" s="19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D155" s="20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="19" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B156" s="19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C156" s="19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D156" s="20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B157" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C157" s="19"/>
-      <c r="D157" s="20" t="s">
+    <row r="157" spans="1:4" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="B157" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="C157" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D157" s="39" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="19" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B158" s="19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C158" s="19" t="s">
         <v>58</v>
@@ -3459,92 +3503,90 @@
       </c>
     </row>
     <row r="159" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
+      <c r="A159" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B159" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C159" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="D159" s="20" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="160" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="B160" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C160" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D160" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="B161" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C161" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D161" s="22" t="s">
-        <v>8</v>
+      <c r="A160" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B160" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C160" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="D160" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B161" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C161" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="D161" s="20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="B162" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C162" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D162" s="22" t="s">
-        <v>8</v>
+      <c r="A162" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="B162" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C162" s="19"/>
+      <c r="D162" s="20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="B163" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C163" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D163" s="22" t="s">
-        <v>8</v>
+      <c r="A163" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B163" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C163" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D163" s="20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="B164" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C164" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="D164" s="22" t="s">
-        <v>8</v>
-      </c>
+      <c r="A164" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
     </row>
     <row r="165" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="21" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>8</v>
@@ -3552,13 +3594,13 @@
     </row>
     <row r="166" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="21" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D166" s="22" t="s">
         <v>8</v>
@@ -3566,13 +3608,13 @@
     </row>
     <row r="167" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="21" t="s">
-        <v>197</v>
+        <v>261</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D167" s="22" t="s">
         <v>8</v>
@@ -3580,13 +3622,13 @@
     </row>
     <row r="168" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="21" t="s">
-        <v>198</v>
+        <v>262</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D168" s="22" t="s">
         <v>8</v>
@@ -3594,27 +3636,27 @@
     </row>
     <row r="169" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="21" t="s">
-        <v>199</v>
+        <v>263</v>
       </c>
       <c r="B169" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="D169" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="21" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="B170" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D170" s="22" t="s">
         <v>8</v>
@@ -3622,13 +3664,13 @@
     </row>
     <row r="171" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="21" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B171" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C171" s="21" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D171" s="22" t="s">
         <v>8</v>
@@ -3636,706 +3678,888 @@
     </row>
     <row r="172" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="21" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B172" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C172" s="21" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="D172" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B173" s="2"/>
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
+      <c r="A173" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="B173" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C173" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D173" s="22" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="174" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="B174" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C174" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="D174" s="24" t="s">
+      <c r="A174" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="B174" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C174" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D174" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="B175" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C175" s="23" t="s">
+      <c r="A175" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="D175" s="24" t="s">
+      <c r="B175" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C175" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D175" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="B176" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C176" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="D176" s="24" t="s">
+      <c r="A176" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="B176" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C176" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D176" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="B177" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C177" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="D177" s="24" t="s">
+      <c r="A177" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="B177" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C177" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D177" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="B178" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C178" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="D178" s="24" t="s">
+      <c r="A178" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="B178" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C178" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D178" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="B179" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C179" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="D179" s="24" t="s">
-        <v>8</v>
+      <c r="A179" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B179" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C179" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D179" s="22" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="B180" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C180" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="D180" s="24" t="s">
-        <v>12</v>
+      <c r="A180" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="B180" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C180" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D180" s="22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="B181" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C181" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="D181" s="24" t="s">
-        <v>12</v>
+      <c r="A181" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="B181" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C181" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D181" s="22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="B182" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C182" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="D182" s="24" t="s">
-        <v>12</v>
+      <c r="A182" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B182" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C182" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D182" s="22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="B183" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C183" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="D183" s="24" t="s">
+      <c r="A183" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B183" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C183" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D183" s="22" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="B184" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C184" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="D184" s="24" t="s">
-        <v>12</v>
-      </c>
+      <c r="A184" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
     </row>
     <row r="185" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="23" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="B185" s="23" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C185" s="23" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D185" s="24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="B186" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C186" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D186" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="B187" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C187" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="D187" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="B188" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C188" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D188" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="B189" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C189" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D189" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="B190" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C190" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D190" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="B191" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C191" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D191" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="B192" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C192" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D192" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="B193" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C193" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="D193" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="B194" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C194" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="D194" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="B195" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C195" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="D195" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="B196" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C196" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="D196" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="B197" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C197" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="D197" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="B198" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C198" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="D198" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+    </row>
+    <row r="200" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="B200" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C200" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D200" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="B201" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C201" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D201" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="B202" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C202" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D202" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="B203" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C203" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D203" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="B186" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C186" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="D186" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="2" t="s">
+      <c r="B204" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C204" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D204" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="B187" s="2"/>
-      <c r="C187" s="2"/>
-      <c r="D187" s="2"/>
-    </row>
-    <row r="188" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="25" t="s">
+      <c r="B205" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C205" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="B188" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C188" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D188" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="25" t="s">
+      <c r="D205" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="B189" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C189" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D189" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="25" t="s">
+      <c r="B206" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C206" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="B190" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C190" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D190" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="25" t="s">
+      <c r="D206" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="B191" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C191" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D191" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="25" t="s">
+      <c r="B207" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C207" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D207" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="B192" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C192" s="25" t="s">
+      <c r="B208" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C208" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D208" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="25" t="s">
         <v>226</v>
       </c>
-      <c r="D192" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="25" t="s">
+      <c r="B209" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C209" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D209" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="B193" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C193" s="25" t="s">
+      <c r="B210" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C210" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D210" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D193" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="25" t="s">
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
+    </row>
+    <row r="212" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="B194" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C194" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D194" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="25" t="s">
+      <c r="B212" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="B195" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C195" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="D195" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="25" t="s">
+      <c r="C212" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D212" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B213" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C213" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D213" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="B196" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C196" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D196" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="25" t="s">
+      <c r="B214" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C214" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D214" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B197" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C197" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="D197" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="2" t="s">
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+    </row>
+    <row r="216" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
-    </row>
-    <row r="199" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="27" t="s">
+      <c r="B216" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C216" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D216" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="B199" s="27" t="s">
+      <c r="B217" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C217" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D217" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="C199" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="D199" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="B200" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="C200" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="D200" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="27" t="s">
+      <c r="B218" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C218" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D218" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="B201" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="C201" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="D201" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="2" t="s">
+      <c r="B219" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C219" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D219" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="B202" s="2"/>
-      <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
-    </row>
-    <row r="203" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="29" t="s">
+      <c r="B220" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C220" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D220" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="B203" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C203" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D203" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="29" t="s">
+      <c r="B221" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C221" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D221" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="B204" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C204" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D204" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="29" t="s">
+      <c r="B222" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C222" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D222" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="B223" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C223" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D223" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="B205" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C205" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D205" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="29" t="s">
+      <c r="B224" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C224" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D224" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="B206" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C206" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D206" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="29" t="s">
+      <c r="B225" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C225" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D225" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B207" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C207" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D207" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="29" t="s">
+      <c r="B226" s="2"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
+    </row>
+    <row r="227" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B227" s="31" t="s">
         <v>243</v>
       </c>
-      <c r="B208" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C208" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D208" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="29" t="s">
+      <c r="C227" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D227" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="B228" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C228" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D228" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="B229" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C229" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D229" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="B230" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C230" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D230" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="B231" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C231" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D231" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="B232" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C232" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D232" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="B233" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C233" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D233" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="B209" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C209" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D209" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="29" t="s">
+      <c r="B234" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C234" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D234" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="B210" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C210" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D210" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="29" t="s">
+      <c r="B235" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C235" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D235" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="B211" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C211" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D211" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B212" s="2"/>
-      <c r="C212" s="2"/>
-      <c r="D212" s="2"/>
-    </row>
-    <row r="213" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="B213" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C213" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D213" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="31" t="s">
-        <v>254</v>
-      </c>
-      <c r="B214" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C214" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D214" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="B215" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C215" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D215" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="B216" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C216" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D216" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="B217" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C217" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D217" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="B218" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C218" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D218" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A219" s="31" t="s">
-        <v>253</v>
-      </c>
-      <c r="B219" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C219" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D219" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="B220" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C220" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D220" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="31" t="s">
-        <v>250</v>
-      </c>
-      <c r="B221" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C221" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D221" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="31" t="s">
-        <v>251</v>
-      </c>
-      <c r="B222" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C222" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D222" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B236" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C236" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D236" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="241" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="242" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="243" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5083,6 +5307,20 @@
     <row r="985" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="986" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="987" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA27691-C726-0C47-8ED5-DDAE3C2F7C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B395C13-9947-BD4E-B82C-5A52C8471F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="14420" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Übungsliste" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="274">
   <si>
     <t>Übung</t>
   </si>
@@ -1336,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1001"/>
+  <dimension ref="A1:D1003"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -4123,18 +4123,18 @@
         <v>202</v>
       </c>
       <c r="D204" s="26" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="25" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B205" s="25" t="s">
         <v>190</v>
       </c>
       <c r="C205" s="25" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="D205" s="26" t="s">
         <v>8</v>
@@ -4142,13 +4142,13 @@
     </row>
     <row r="206" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B206" s="25" t="s">
         <v>190</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D206" s="26" t="s">
         <v>8</v>
@@ -4156,13 +4156,13 @@
     </row>
     <row r="207" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B207" s="25" t="s">
         <v>190</v>
       </c>
       <c r="C207" s="25" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="D207" s="26" t="s">
         <v>8</v>
@@ -4170,13 +4170,13 @@
     </row>
     <row r="208" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B208" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="C208" s="27" t="s">
-        <v>156</v>
+      <c r="C208" s="25" t="s">
+        <v>202</v>
       </c>
       <c r="D208" s="26" t="s">
         <v>12</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="209" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B209" s="25" t="s">
         <v>190</v>
@@ -4198,7 +4198,7 @@
     </row>
     <row r="210" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="25" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B210" s="25" t="s">
         <v>190</v>
@@ -4211,44 +4211,44 @@
       </c>
     </row>
     <row r="211" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B211" s="2"/>
-      <c r="C211" s="2"/>
-      <c r="D211" s="2"/>
+      <c r="A211" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="B211" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C211" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D211" s="26" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="212" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="B212" s="27" t="s">
-        <v>230</v>
+      <c r="A212" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="B212" s="25" t="s">
+        <v>190</v>
       </c>
       <c r="C212" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="D212" s="28" t="s">
+      <c r="D212" s="26" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="B213" s="27" t="s">
-        <v>230</v>
-      </c>
-      <c r="C213" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="D213" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="A213" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
     </row>
     <row r="214" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="27" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B214" s="27" t="s">
         <v>230</v>
@@ -4261,44 +4261,44 @@
       </c>
     </row>
     <row r="215" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="2" t="s">
+      <c r="A215" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B215" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C215" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D215" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="B216" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C216" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D216" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B215" s="2"/>
-      <c r="C215" s="2"/>
-      <c r="D215" s="2"/>
-    </row>
-    <row r="216" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="29" t="s">
-        <v>233</v>
-      </c>
-      <c r="B216" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="C216" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="D216" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="B217" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="C217" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="D217" s="30" t="s">
-        <v>12</v>
-      </c>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
     </row>
     <row r="218" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="29" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B218" s="29" t="s">
         <v>211</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="219" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B219" s="29" t="s">
         <v>211</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="220" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="29" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B220" s="29" t="s">
         <v>211</v>
@@ -4340,7 +4340,7 @@
     </row>
     <row r="221" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="29" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B221" s="29" t="s">
         <v>211</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="222" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="29" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B222" s="29" t="s">
         <v>211</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="223" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="29" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="B223" s="29" t="s">
         <v>211</v>
@@ -4382,7 +4382,7 @@
     </row>
     <row r="224" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="29" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B224" s="29" t="s">
         <v>211</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="225" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="B225" s="29" t="s">
         <v>211</v>
@@ -4409,44 +4409,44 @@
       </c>
     </row>
     <row r="226" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="2" t="s">
+      <c r="A226" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="B226" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C226" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D226" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="B227" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C227" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D227" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B226" s="2"/>
-      <c r="C226" s="2"/>
-      <c r="D226" s="2"/>
-    </row>
-    <row r="227" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A227" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="B227" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="C227" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="D227" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A228" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="B228" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="C228" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="D228" s="32" t="s">
-        <v>12</v>
-      </c>
+      <c r="B228" s="2"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
     </row>
     <row r="229" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="31" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B229" s="31" t="s">
         <v>243</v>
@@ -4460,7 +4460,7 @@
     </row>
     <row r="230" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B230" s="31" t="s">
         <v>243</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="231" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="31" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B231" s="31" t="s">
         <v>243</v>
@@ -4488,7 +4488,7 @@
     </row>
     <row r="232" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="31" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B232" s="31" t="s">
         <v>243</v>
@@ -4502,7 +4502,7 @@
     </row>
     <row r="233" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="31" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B233" s="31" t="s">
         <v>243</v>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="234" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="31" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B234" s="31" t="s">
         <v>243</v>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="235" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="31" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B235" s="31" t="s">
         <v>243</v>
@@ -4544,7 +4544,7 @@
     </row>
     <row r="236" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="31" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B236" s="31" t="s">
         <v>243</v>
@@ -4556,8 +4556,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="31" t="s">
+        <v>245</v>
+      </c>
+      <c r="B237" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C237" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D237" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="B238" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C238" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D238" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="239" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="240" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="241" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5321,6 +5347,8 @@
     <row r="999" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B395C13-9947-BD4E-B82C-5A52C8471F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941F4702-0DFE-F542-94EF-4CE8FDB1ACB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Übungsliste" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="276">
   <si>
     <t>Übung</t>
   </si>
@@ -842,6 +842,12 @@
   </si>
   <si>
     <t>LH Back Extensions</t>
+  </si>
+  <si>
+    <t>LH Hip Thrusts</t>
+  </si>
+  <si>
+    <t>Multipresse Hip Thrusts</t>
   </si>
 </sst>
 </file>
@@ -4114,7 +4120,7 @@
     </row>
     <row r="204" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="25" t="s">
-        <v>219</v>
+        <v>274</v>
       </c>
       <c r="B204" s="25" t="s">
         <v>190</v>
@@ -4170,7 +4176,7 @@
     </row>
     <row r="208" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="25" t="s">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="B208" s="25" t="s">
         <v>190</v>

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941F4702-0DFE-F542-94EF-4CE8FDB1ACB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78426E77-3CE5-C441-97A7-2AB31C137A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="274">
   <si>
     <t>Übung</t>
   </si>
@@ -842,12 +842,6 @@
   </si>
   <si>
     <t>LH Back Extensions</t>
-  </si>
-  <si>
-    <t>LH Hip Thrusts</t>
-  </si>
-  <si>
-    <t>Multipresse Hip Thrusts</t>
   </si>
 </sst>
 </file>
@@ -1342,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1003"/>
+  <dimension ref="A1:D1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -4120,7 +4114,7 @@
     </row>
     <row r="204" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="25" t="s">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="B204" s="25" t="s">
         <v>190</v>
@@ -4129,18 +4123,18 @@
         <v>202</v>
       </c>
       <c r="D204" s="26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B205" s="25" t="s">
         <v>190</v>
       </c>
       <c r="C205" s="25" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="D205" s="26" t="s">
         <v>8</v>
@@ -4148,13 +4142,13 @@
     </row>
     <row r="206" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="25" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B206" s="25" t="s">
         <v>190</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D206" s="26" t="s">
         <v>8</v>
@@ -4162,13 +4156,13 @@
     </row>
     <row r="207" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="25" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B207" s="25" t="s">
         <v>190</v>
       </c>
       <c r="C207" s="25" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="D207" s="26" t="s">
         <v>8</v>
@@ -4176,13 +4170,13 @@
     </row>
     <row r="208" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="25" t="s">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="B208" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="C208" s="25" t="s">
-        <v>202</v>
+      <c r="C208" s="27" t="s">
+        <v>156</v>
       </c>
       <c r="D208" s="26" t="s">
         <v>12</v>
@@ -4190,7 +4184,7 @@
     </row>
     <row r="209" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="25" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B209" s="25" t="s">
         <v>190</v>
@@ -4204,7 +4198,7 @@
     </row>
     <row r="210" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="25" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B210" s="25" t="s">
         <v>190</v>
@@ -4217,44 +4211,44 @@
       </c>
     </row>
     <row r="211" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="B211" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="C211" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="D211" s="26" t="s">
-        <v>8</v>
-      </c>
+      <c r="A211" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
     </row>
     <row r="212" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="B212" s="25" t="s">
-        <v>190</v>
+      <c r="A212" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="B212" s="27" t="s">
+        <v>230</v>
       </c>
       <c r="C212" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="D212" s="26" t="s">
+      <c r="D212" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B213" s="2"/>
-      <c r="C213" s="2"/>
-      <c r="D213" s="2"/>
+      <c r="A213" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B213" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C213" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D213" s="28" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="214" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="27" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B214" s="27" t="s">
         <v>230</v>
@@ -4267,44 +4261,44 @@
       </c>
     </row>
     <row r="215" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="B215" s="27" t="s">
-        <v>230</v>
-      </c>
-      <c r="C215" s="27" t="s">
+      <c r="A215" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+    </row>
+    <row r="216" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="B216" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C216" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="D215" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="B216" s="27" t="s">
-        <v>230</v>
-      </c>
-      <c r="C216" s="27" t="s">
+      <c r="D216" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="B217" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C217" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="D216" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B217" s="2"/>
-      <c r="C217" s="2"/>
-      <c r="D217" s="2"/>
+      <c r="D217" s="30" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="218" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="29" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B218" s="29" t="s">
         <v>211</v>
@@ -4318,7 +4312,7 @@
     </row>
     <row r="219" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="29" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B219" s="29" t="s">
         <v>211</v>
@@ -4332,7 +4326,7 @@
     </row>
     <row r="220" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="29" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B220" s="29" t="s">
         <v>211</v>
@@ -4346,7 +4340,7 @@
     </row>
     <row r="221" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="29" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B221" s="29" t="s">
         <v>211</v>
@@ -4360,7 +4354,7 @@
     </row>
     <row r="222" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="29" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B222" s="29" t="s">
         <v>211</v>
@@ -4374,7 +4368,7 @@
     </row>
     <row r="223" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="29" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="B223" s="29" t="s">
         <v>211</v>
@@ -4388,7 +4382,7 @@
     </row>
     <row r="224" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B224" s="29" t="s">
         <v>211</v>
@@ -4402,7 +4396,7 @@
     </row>
     <row r="225" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="B225" s="29" t="s">
         <v>211</v>
@@ -4415,44 +4409,44 @@
       </c>
     </row>
     <row r="226" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="B226" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="C226" s="29" t="s">
+      <c r="A226" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B226" s="2"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
+    </row>
+    <row r="227" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B227" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C227" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="D226" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A227" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="B227" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="C227" s="29" t="s">
+      <c r="D227" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="B228" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C228" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="D227" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A228" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B228" s="2"/>
-      <c r="C228" s="2"/>
-      <c r="D228" s="2"/>
+      <c r="D228" s="32" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="229" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="31" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B229" s="31" t="s">
         <v>243</v>
@@ -4466,7 +4460,7 @@
     </row>
     <row r="230" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B230" s="31" t="s">
         <v>243</v>
@@ -4480,7 +4474,7 @@
     </row>
     <row r="231" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B231" s="31" t="s">
         <v>243</v>
@@ -4494,7 +4488,7 @@
     </row>
     <row r="232" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="31" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B232" s="31" t="s">
         <v>243</v>
@@ -4508,7 +4502,7 @@
     </row>
     <row r="233" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="31" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B233" s="31" t="s">
         <v>243</v>
@@ -4522,7 +4516,7 @@
     </row>
     <row r="234" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="31" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B234" s="31" t="s">
         <v>243</v>
@@ -4536,7 +4530,7 @@
     </row>
     <row r="235" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="31" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B235" s="31" t="s">
         <v>243</v>
@@ -4550,7 +4544,7 @@
     </row>
     <row r="236" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B236" s="31" t="s">
         <v>243</v>
@@ -4562,34 +4556,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="B237" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="C237" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="D237" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="B238" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="C238" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="D238" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
+    <row r="237" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="239" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="240" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="241" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5353,8 +5321,6 @@
     <row r="999" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78426E77-3CE5-C441-97A7-2AB31C137A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C2959B-E2B1-AE48-B49F-D4A6C9C8B153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -226,9 +226,6 @@
     <t>Kabel Shruggs</t>
   </si>
   <si>
-    <t>KH Rudern, Brustgestützt, Obergriff</t>
-  </si>
-  <si>
     <t>Lat, Bizeps</t>
   </si>
   <si>
@@ -256,9 +253,6 @@
     <t>Multipresse Rudern, schulterbreit, Untergriff</t>
   </si>
   <si>
-    <t>Multipresse Rudern, schulterbreiteit, Obergriff</t>
-  </si>
-  <si>
     <t>Multipresse Shruggs</t>
   </si>
   <si>
@@ -842,6 +836,12 @@
   </si>
   <si>
     <t>LH Back Extensions</t>
+  </si>
+  <si>
+    <t>Multipresse Rudern, schulterbreit, Obergriff</t>
+  </si>
+  <si>
+    <t>KH Rudern, Obergriff</t>
   </si>
 </sst>
 </file>
@@ -1966,7 +1966,7 @@
     </row>
     <row r="46" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>14</v>
@@ -2043,14 +2043,14 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="34" t="s">
-        <v>68</v>
+      <c r="A52" s="7" t="s">
+        <v>273</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>8</v>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="53" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>63</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="54" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>63</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="55" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>63</v>
@@ -2100,13 +2100,13 @@
     </row>
     <row r="56" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>8</v>
@@ -2114,7 +2114,7 @@
     </row>
     <row r="57" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>63</v>
@@ -2128,7 +2128,7 @@
     </row>
     <row r="58" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>63</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="59" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>63</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="60" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>63</v>
@@ -2170,21 +2170,21 @@
     </row>
     <row r="61" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="34" t="s">
-        <v>78</v>
+      <c r="A62" s="7" t="s">
+        <v>272</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>63</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="63" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>63</v>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="64" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>63</v>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="65" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>63</v>
@@ -2240,7 +2240,7 @@
     </row>
     <row r="66" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>63</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="67" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>63</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="68" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>63</v>
@@ -2282,13 +2282,13 @@
     </row>
     <row r="69" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>8</v>
@@ -2296,7 +2296,7 @@
     </row>
     <row r="70" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>63</v>
@@ -2310,13 +2310,13 @@
     </row>
     <row r="71" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>8</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="72" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>63</v>
@@ -2338,7 +2338,7 @@
     </row>
     <row r="73" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -2346,13 +2346,13 @@
     </row>
     <row r="74" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>12</v>
@@ -2360,13 +2360,13 @@
     </row>
     <row r="75" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>12</v>
@@ -2374,13 +2374,13 @@
     </row>
     <row r="76" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>8</v>
@@ -2388,13 +2388,13 @@
     </row>
     <row r="77" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>8</v>
@@ -2402,13 +2402,13 @@
     </row>
     <row r="78" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>12</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="79" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>12</v>
@@ -2430,13 +2430,13 @@
     </row>
     <row r="80" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>8</v>
@@ -2444,13 +2444,13 @@
     </row>
     <row r="81" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>12</v>
@@ -2458,13 +2458,13 @@
     </row>
     <row r="82" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>8</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="83" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>8</v>
@@ -2486,13 +2486,13 @@
     </row>
     <row r="84" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B84" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>8</v>
@@ -2500,13 +2500,13 @@
     </row>
     <row r="85" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B85" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>12</v>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="86" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="87" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C87" s="11" t="s">
         <v>52</v>
@@ -2536,13 +2536,13 @@
     </row>
     <row r="88" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>12</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="89" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>52</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="90" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C90" s="13"/>
       <c r="D90" s="14" t="s">
@@ -2576,13 +2576,13 @@
     </row>
     <row r="91" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D91" s="12" t="s">
         <v>12</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="92" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>52</v>
@@ -2604,13 +2604,13 @@
     </row>
     <row r="93" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>8</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="94" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>52</v>
@@ -2632,13 +2632,13 @@
     </row>
     <row r="95" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D95" s="12" t="s">
         <v>8</v>
@@ -2646,13 +2646,13 @@
     </row>
     <row r="96" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D96" s="12" t="s">
         <v>8</v>
@@ -2660,13 +2660,13 @@
     </row>
     <row r="97" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D97" s="12" t="s">
         <v>12</v>
@@ -2674,13 +2674,13 @@
     </row>
     <row r="98" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D98" s="12" t="s">
         <v>8</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="99" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D99" s="12" t="s">
         <v>12</v>
@@ -2702,10 +2702,10 @@
     </row>
     <row r="100" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>52</v>
@@ -2716,7 +2716,7 @@
     </row>
     <row r="101" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="102" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B102" s="13" t="s">
         <v>64</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="103" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="13" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B103" s="13" t="s">
         <v>64</v>
@@ -2752,7 +2752,7 @@
     </row>
     <row r="104" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B104" s="13" t="s">
         <v>64</v>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="105" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B105" s="13" t="s">
         <v>64</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="106" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B106" s="13" t="s">
         <v>64</v>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="107" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B107" s="13" t="s">
         <v>64</v>
@@ -2808,7 +2808,7 @@
     </row>
     <row r="108" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B108" s="13" t="s">
         <v>64</v>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="109" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -2830,13 +2830,13 @@
     </row>
     <row r="110" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B110" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D110" s="16" t="s">
         <v>12</v>
@@ -2844,13 +2844,13 @@
     </row>
     <row r="111" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B111" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D111" s="16" t="s">
         <v>12</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B112" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D112" s="16" t="s">
         <v>12</v>
@@ -2872,13 +2872,13 @@
     </row>
     <row r="113" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B113" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D113" s="16" t="s">
         <v>12</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="114" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="15" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B114" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D114" s="16" t="s">
         <v>12</v>
@@ -2900,13 +2900,13 @@
     </row>
     <row r="115" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B115" s="36" t="s">
         <v>58</v>
       </c>
       <c r="C115" s="36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D115" s="37" t="s">
         <v>12</v>
@@ -2914,13 +2914,13 @@
     </row>
     <row r="116" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B116" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D116" s="16" t="s">
         <v>12</v>
@@ -2928,13 +2928,13 @@
     </row>
     <row r="117" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B117" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D117" s="16" t="s">
         <v>12</v>
@@ -2942,13 +2942,13 @@
     </row>
     <row r="118" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B118" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D118" s="16" t="s">
         <v>12</v>
@@ -2956,13 +2956,13 @@
     </row>
     <row r="119" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B119" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D119" s="16" t="s">
         <v>12</v>
@@ -2970,13 +2970,13 @@
     </row>
     <row r="120" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B120" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D120" s="16" t="s">
         <v>12</v>
@@ -2984,13 +2984,13 @@
     </row>
     <row r="121" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="15" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B121" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D121" s="16" t="s">
         <v>12</v>
@@ -2998,13 +2998,13 @@
     </row>
     <row r="122" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B122" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D122" s="16" t="s">
         <v>12</v>
@@ -3012,13 +3012,13 @@
     </row>
     <row r="123" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B123" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D123" s="16" t="s">
         <v>12</v>
@@ -3026,13 +3026,13 @@
     </row>
     <row r="124" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B124" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D124" s="16" t="s">
         <v>12</v>
@@ -3040,13 +3040,13 @@
     </row>
     <row r="125" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B125" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D125" s="16" t="s">
         <v>12</v>
@@ -3054,13 +3054,13 @@
     </row>
     <row r="126" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="15" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B126" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D126" s="16" t="s">
         <v>12</v>
@@ -3068,13 +3068,13 @@
     </row>
     <row r="127" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B127" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D127" s="16" t="s">
         <v>12</v>
@@ -3082,13 +3082,13 @@
     </row>
     <row r="128" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B128" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D128" s="16" t="s">
         <v>12</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="129" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B129" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D129" s="16" t="s">
         <v>12</v>
@@ -3110,13 +3110,13 @@
     </row>
     <row r="130" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B130" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D130" s="16" t="s">
         <v>12</v>
@@ -3124,13 +3124,13 @@
     </row>
     <row r="131" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B131" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D131" s="16" t="s">
         <v>12</v>
@@ -3138,13 +3138,13 @@
     </row>
     <row r="132" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B132" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D132" s="16" t="s">
         <v>12</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="133" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -3160,13 +3160,13 @@
     </row>
     <row r="134" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B134" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C134" s="17" t="s">
         <v>151</v>
-      </c>
-      <c r="B134" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C134" s="17" t="s">
-        <v>153</v>
       </c>
       <c r="D134" s="18" t="s">
         <v>8</v>
@@ -3174,13 +3174,13 @@
     </row>
     <row r="135" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D135" s="18" t="s">
         <v>8</v>
@@ -3188,13 +3188,13 @@
     </row>
     <row r="136" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D136" s="18" t="s">
         <v>12</v>
@@ -3202,13 +3202,13 @@
     </row>
     <row r="137" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="17" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D137" s="18" t="s">
         <v>12</v>
@@ -3216,13 +3216,13 @@
     </row>
     <row r="138" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C138" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D138" s="18" t="s">
         <v>12</v>
@@ -3230,13 +3230,13 @@
     </row>
     <row r="139" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D139" s="18" t="s">
         <v>12</v>
@@ -3244,13 +3244,13 @@
     </row>
     <row r="140" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D140" s="18" t="s">
         <v>12</v>
@@ -3258,13 +3258,13 @@
     </row>
     <row r="141" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D141" s="18" t="s">
         <v>12</v>
@@ -3272,13 +3272,13 @@
     </row>
     <row r="142" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D142" s="18" t="s">
         <v>12</v>
@@ -3286,13 +3286,13 @@
     </row>
     <row r="143" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D143" s="18" t="s">
         <v>12</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="144" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D144" s="18" t="s">
         <v>12</v>
@@ -3314,13 +3314,13 @@
     </row>
     <row r="145" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D145" s="18" t="s">
         <v>12</v>
@@ -3328,13 +3328,13 @@
     </row>
     <row r="146" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D146" s="18" t="s">
         <v>8</v>
@@ -3342,13 +3342,13 @@
     </row>
     <row r="147" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D147" s="18" t="s">
         <v>8</v>
@@ -3356,13 +3356,13 @@
     </row>
     <row r="148" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="17" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D148" s="18" t="s">
         <v>12</v>
@@ -3370,13 +3370,13 @@
     </row>
     <row r="149" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C149" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D149" s="18" t="s">
         <v>12</v>
@@ -3384,13 +3384,13 @@
     </row>
     <row r="150" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C150" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D150" s="18" t="s">
         <v>12</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="151" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -3406,13 +3406,13 @@
     </row>
     <row r="152" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="19" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B152" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C152" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D152" s="20" t="s">
         <v>12</v>
@@ -3420,10 +3420,10 @@
     </row>
     <row r="153" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="19" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B153" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C153" s="19" t="s">
         <v>58</v>
@@ -3434,13 +3434,13 @@
     </row>
     <row r="154" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B154" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C154" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D154" s="20" t="s">
         <v>12</v>
@@ -3448,13 +3448,13 @@
     </row>
     <row r="155" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="19" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B155" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D155" s="20" t="s">
         <v>12</v>
@@ -3462,13 +3462,13 @@
     </row>
     <row r="156" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B156" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C156" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D156" s="20" t="s">
         <v>12</v>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="157" spans="1:4" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="38" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B157" s="38" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C157" s="38" t="s">
         <v>58</v>
@@ -3490,10 +3490,10 @@
     </row>
     <row r="158" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B158" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C158" s="19" t="s">
         <v>58</v>
@@ -3504,13 +3504,13 @@
     </row>
     <row r="159" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="19" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B159" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C159" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D159" s="20" t="s">
         <v>12</v>
@@ -3518,13 +3518,13 @@
     </row>
     <row r="160" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="19" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B160" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C160" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D160" s="20" t="s">
         <v>12</v>
@@ -3532,13 +3532,13 @@
     </row>
     <row r="161" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="19" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B161" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C161" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D161" s="20" t="s">
         <v>12</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="162" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="19" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B162" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C162" s="19"/>
       <c r="D162" s="20" t="s">
@@ -3558,10 +3558,10 @@
     </row>
     <row r="163" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="19" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B163" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C163" s="19" t="s">
         <v>58</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="164" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -3580,13 +3580,13 @@
     </row>
     <row r="165" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="B165" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="C165" s="21" t="s">
         <v>183</v>
-      </c>
-      <c r="B165" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="C165" s="21" t="s">
-        <v>185</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>8</v>
@@ -3594,13 +3594,13 @@
     </row>
     <row r="166" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D166" s="22" t="s">
         <v>8</v>
@@ -3608,13 +3608,13 @@
     </row>
     <row r="167" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D167" s="22" t="s">
         <v>8</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="168" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D168" s="22" t="s">
         <v>8</v>
@@ -3636,13 +3636,13 @@
     </row>
     <row r="169" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B169" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D169" s="22" t="s">
         <v>8</v>
@@ -3650,13 +3650,13 @@
     </row>
     <row r="170" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B170" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D170" s="22" t="s">
         <v>8</v>
@@ -3664,13 +3664,13 @@
     </row>
     <row r="171" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B171" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C171" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D171" s="22" t="s">
         <v>8</v>
@@ -3678,13 +3678,13 @@
     </row>
     <row r="172" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B172" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C172" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D172" s="22" t="s">
         <v>8</v>
@@ -3692,13 +3692,13 @@
     </row>
     <row r="173" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B173" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C173" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D173" s="22" t="s">
         <v>8</v>
@@ -3706,13 +3706,13 @@
     </row>
     <row r="174" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="21" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B174" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C174" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D174" s="22" t="s">
         <v>8</v>
@@ -3720,13 +3720,13 @@
     </row>
     <row r="175" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B175" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C175" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D175" s="22" t="s">
         <v>8</v>
@@ -3734,13 +3734,13 @@
     </row>
     <row r="176" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="21" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B176" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C176" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D176" s="22" t="s">
         <v>8</v>
@@ -3748,13 +3748,13 @@
     </row>
     <row r="177" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B177" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C177" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D177" s="22" t="s">
         <v>8</v>
@@ -3762,13 +3762,13 @@
     </row>
     <row r="178" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B178" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C178" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D178" s="22" t="s">
         <v>8</v>
@@ -3776,13 +3776,13 @@
     </row>
     <row r="179" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="21" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B179" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C179" s="21" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D179" s="22" t="s">
         <v>12</v>
@@ -3790,13 +3790,13 @@
     </row>
     <row r="180" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="21" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B180" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C180" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D180" s="22" t="s">
         <v>8</v>
@@ -3804,13 +3804,13 @@
     </row>
     <row r="181" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="21" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B181" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C181" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D181" s="22" t="s">
         <v>8</v>
@@ -3818,13 +3818,13 @@
     </row>
     <row r="182" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B182" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C182" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D182" s="22" t="s">
         <v>8</v>
@@ -3832,13 +3832,13 @@
     </row>
     <row r="183" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="21" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B183" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C183" s="21" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D183" s="22" t="s">
         <v>12</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="184" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -3854,13 +3854,13 @@
     </row>
     <row r="185" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="B185" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="C185" s="23" t="s">
         <v>201</v>
-      </c>
-      <c r="B185" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="C185" s="23" t="s">
-        <v>203</v>
       </c>
       <c r="D185" s="24" t="s">
         <v>8</v>
@@ -3868,13 +3868,13 @@
     </row>
     <row r="186" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="23" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B186" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C186" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D186" s="24" t="s">
         <v>8</v>
@@ -3882,13 +3882,13 @@
     </row>
     <row r="187" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="23" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B187" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C187" s="23" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D187" s="24" t="s">
         <v>8</v>
@@ -3896,13 +3896,13 @@
     </row>
     <row r="188" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="23" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B188" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C188" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D188" s="24" t="s">
         <v>8</v>
@@ -3910,13 +3910,13 @@
     </row>
     <row r="189" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="23" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B189" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C189" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D189" s="24" t="s">
         <v>8</v>
@@ -3924,13 +3924,13 @@
     </row>
     <row r="190" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="23" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B190" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C190" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D190" s="24" t="s">
         <v>8</v>
@@ -3938,13 +3938,13 @@
     </row>
     <row r="191" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="23" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B191" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C191" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D191" s="24" t="s">
         <v>8</v>
@@ -3952,13 +3952,13 @@
     </row>
     <row r="192" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="23" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B192" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C192" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D192" s="24" t="s">
         <v>12</v>
@@ -3966,13 +3966,13 @@
     </row>
     <row r="193" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B193" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C193" s="23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D193" s="24" t="s">
         <v>12</v>
@@ -3980,13 +3980,13 @@
     </row>
     <row r="194" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="23" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B194" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C194" s="23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D194" s="24" t="s">
         <v>12</v>
@@ -3994,13 +3994,13 @@
     </row>
     <row r="195" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="23" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B195" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C195" s="23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D195" s="24" t="s">
         <v>12</v>
@@ -4008,13 +4008,13 @@
     </row>
     <row r="196" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="23" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B196" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C196" s="23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D196" s="24" t="s">
         <v>12</v>
@@ -4022,13 +4022,13 @@
     </row>
     <row r="197" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B197" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C197" s="23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D197" s="24" t="s">
         <v>12</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="198" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="23" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B198" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C198" s="23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D198" s="24" t="s">
         <v>12</v>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="199" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -4058,13 +4058,13 @@
     </row>
     <row r="200" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="25" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B200" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C200" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D200" s="26" t="s">
         <v>12</v>
@@ -4072,13 +4072,13 @@
     </row>
     <row r="201" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="25" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B201" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C201" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D201" s="26" t="s">
         <v>12</v>
@@ -4086,13 +4086,13 @@
     </row>
     <row r="202" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="25" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B202" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C202" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D202" s="26" t="s">
         <v>12</v>
@@ -4100,13 +4100,13 @@
     </row>
     <row r="203" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B203" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C203" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D203" s="26" t="s">
         <v>12</v>
@@ -4114,13 +4114,13 @@
     </row>
     <row r="204" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B204" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C204" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D204" s="26" t="s">
         <v>8</v>
@@ -4128,13 +4128,13 @@
     </row>
     <row r="205" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B205" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C205" s="25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D205" s="26" t="s">
         <v>8</v>
@@ -4142,13 +4142,13 @@
     </row>
     <row r="206" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B206" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D206" s="26" t="s">
         <v>8</v>
@@ -4156,13 +4156,13 @@
     </row>
     <row r="207" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B207" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C207" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D207" s="26" t="s">
         <v>8</v>
@@ -4170,13 +4170,13 @@
     </row>
     <row r="208" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="25" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B208" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C208" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D208" s="26" t="s">
         <v>12</v>
@@ -4184,13 +4184,13 @@
     </row>
     <row r="209" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B209" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C209" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D209" s="26" t="s">
         <v>8</v>
@@ -4198,13 +4198,13 @@
     </row>
     <row r="210" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="25" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B210" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C210" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D210" s="26" t="s">
         <v>12</v>
@@ -4212,7 +4212,7 @@
     </row>
     <row r="211" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -4220,13 +4220,13 @@
     </row>
     <row r="212" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="27" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B212" s="27" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C212" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D212" s="28" t="s">
         <v>12</v>
@@ -4234,13 +4234,13 @@
     </row>
     <row r="213" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="27" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B213" s="27" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C213" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D213" s="28" t="s">
         <v>12</v>
@@ -4248,13 +4248,13 @@
     </row>
     <row r="214" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="27" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B214" s="27" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C214" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D214" s="28" t="s">
         <v>12</v>
@@ -4262,7 +4262,7 @@
     </row>
     <row r="215" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -4270,13 +4270,13 @@
     </row>
     <row r="216" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="29" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B216" s="29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C216" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D216" s="30" t="s">
         <v>12</v>
@@ -4284,13 +4284,13 @@
     </row>
     <row r="217" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B217" s="29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C217" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D217" s="30" t="s">
         <v>12</v>
@@ -4298,13 +4298,13 @@
     </row>
     <row r="218" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="29" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B218" s="29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C218" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D218" s="30" t="s">
         <v>12</v>
@@ -4312,13 +4312,13 @@
     </row>
     <row r="219" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B219" s="29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C219" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D219" s="30" t="s">
         <v>12</v>
@@ -4326,13 +4326,13 @@
     </row>
     <row r="220" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="29" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B220" s="29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C220" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D220" s="30" t="s">
         <v>12</v>
@@ -4340,13 +4340,13 @@
     </row>
     <row r="221" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="29" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B221" s="29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C221" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D221" s="30" t="s">
         <v>12</v>
@@ -4354,13 +4354,13 @@
     </row>
     <row r="222" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="29" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B222" s="29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C222" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D222" s="30" t="s">
         <v>12</v>
@@ -4368,13 +4368,13 @@
     </row>
     <row r="223" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="29" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B223" s="29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C223" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D223" s="30" t="s">
         <v>12</v>
@@ -4382,13 +4382,13 @@
     </row>
     <row r="224" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="29" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B224" s="29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C224" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D224" s="30" t="s">
         <v>12</v>
@@ -4396,13 +4396,13 @@
     </row>
     <row r="225" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B225" s="29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C225" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D225" s="30" t="s">
         <v>12</v>
@@ -4410,7 +4410,7 @@
     </row>
     <row r="226" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -4418,13 +4418,13 @@
     </row>
     <row r="227" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="31" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B227" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C227" s="31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D227" s="32" t="s">
         <v>12</v>
@@ -4432,13 +4432,13 @@
     </row>
     <row r="228" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="31" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B228" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C228" s="31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D228" s="32" t="s">
         <v>12</v>
@@ -4446,13 +4446,13 @@
     </row>
     <row r="229" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="31" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B229" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C229" s="31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D229" s="32" t="s">
         <v>12</v>
@@ -4460,13 +4460,13 @@
     </row>
     <row r="230" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="31" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B230" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C230" s="31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D230" s="32" t="s">
         <v>12</v>
@@ -4474,13 +4474,13 @@
     </row>
     <row r="231" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="31" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B231" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C231" s="31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D231" s="32" t="s">
         <v>12</v>
@@ -4488,13 +4488,13 @@
     </row>
     <row r="232" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="31" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B232" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C232" s="31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D232" s="32" t="s">
         <v>12</v>
@@ -4502,13 +4502,13 @@
     </row>
     <row r="233" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="31" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B233" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C233" s="31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D233" s="32" t="s">
         <v>12</v>
@@ -4516,13 +4516,13 @@
     </row>
     <row r="234" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="31" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B234" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C234" s="31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D234" s="32" t="s">
         <v>12</v>
@@ -4530,13 +4530,13 @@
     </row>
     <row r="235" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="31" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B235" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C235" s="31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D235" s="32" t="s">
         <v>12</v>
@@ -4544,13 +4544,13 @@
     </row>
     <row r="236" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="31" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B236" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C236" s="31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D236" s="32" t="s">
         <v>12</v>

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C2959B-E2B1-AE48-B49F-D4A6C9C8B153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1ED706-312F-8542-B21F-89C23584ADC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Übungsliste" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="261">
   <si>
     <t>Übung</t>
   </si>
@@ -70,9 +70,6 @@
     <t>KH Flachbankdrücken</t>
   </si>
   <si>
-    <t>KH Flachbankdrücken, neutral</t>
-  </si>
-  <si>
     <t>KH Fliegende</t>
   </si>
   <si>
@@ -124,9 +121,6 @@
     <t>PlateLoaded Flachbankdrücken</t>
   </si>
   <si>
-    <t>PlateLoaded Flachbankdrücken, neutral</t>
-  </si>
-  <si>
     <t>PlateLoaded Fliegende</t>
   </si>
   <si>
@@ -142,9 +136,6 @@
     <t>Steck Flachbankdrücken</t>
   </si>
   <si>
-    <t>Steck Flachbankdrücken, neutral</t>
-  </si>
-  <si>
     <t>Steck Fliegende</t>
   </si>
   <si>
@@ -157,39 +148,18 @@
     <t>■ LAT</t>
   </si>
   <si>
-    <t>Kabel Rudern, eng, neutral</t>
-  </si>
-  <si>
     <t>Oberer Rücken, Bizeps, Hintere Schulter</t>
   </si>
   <si>
     <t>Kabel Überzüge, weit (Lat-betont)</t>
   </si>
   <si>
-    <t>KH Rudern, eng, neutral</t>
-  </si>
-  <si>
-    <t>Klimmzug, eng, neutral</t>
-  </si>
-  <si>
     <t>Bizeps, Oberer Rücken</t>
   </si>
   <si>
-    <t>Klimmzug, Obergriff, weit</t>
-  </si>
-  <si>
     <t>Oberer Rücken, Bizeps</t>
   </si>
   <si>
-    <t>Klimmzug, Untergriff, schulterbreit</t>
-  </si>
-  <si>
-    <t>Latziehen in den Nacken, Obergriff, weit</t>
-  </si>
-  <si>
-    <t>Latziehen zur Brust, Obergriff</t>
-  </si>
-  <si>
     <t>Bizeps, Hintere Schulter, Oberer Rücken</t>
   </si>
   <si>
@@ -199,9 +169,6 @@
     <t>Bizeps</t>
   </si>
   <si>
-    <t>Latziehen, schulterbreit, Untergriff</t>
-  </si>
-  <si>
     <t>LH Überzüge, weit (Lat-betont)</t>
   </si>
   <si>
@@ -235,30 +202,12 @@
     <t>KH Trap3Raise</t>
   </si>
   <si>
-    <t>LH Rudern, schulterbreit, Obergriff</t>
-  </si>
-  <si>
-    <t>LH Rudern, schulterbreit, Untergriff</t>
-  </si>
-  <si>
     <t>LH Shruggs</t>
   </si>
   <si>
-    <t>LH T-Bar Rudern eng</t>
-  </si>
-  <si>
-    <t>LH T-Bar Rudern schulterbreit</t>
-  </si>
-  <si>
-    <t>Multipresse Rudern, schulterbreit, Untergriff</t>
-  </si>
-  <si>
     <t>Multipresse Shruggs</t>
   </si>
   <si>
-    <t>PlateLoaded Rudern, schulterbreit, Obergriff</t>
-  </si>
-  <si>
     <t>PlateLoaded T-Bar Rudern</t>
   </si>
   <si>
@@ -268,15 +217,6 @@
     <t>Rudern mit Seil zum Hals</t>
   </si>
   <si>
-    <t>Rudern Multipresse, Brustgestützt, Obergriff</t>
-  </si>
-  <si>
-    <t>Steck Rudern, schulterbreit, Obergriff</t>
-  </si>
-  <si>
-    <t>Steck Rudern, weit, Untergriff</t>
-  </si>
-  <si>
     <t>Y-Raise</t>
   </si>
   <si>
@@ -289,9 +229,6 @@
     <t>Seitliche Schulter</t>
   </si>
   <si>
-    <t>Kabel Frontheben, neutral</t>
-  </si>
-  <si>
     <t>KH Arnoldpresse</t>
   </si>
   <si>
@@ -304,9 +241,6 @@
     <t>KH Frontheben</t>
   </si>
   <si>
-    <t>KH Frontheben, neutral</t>
-  </si>
-  <si>
     <t>LH Frontdrücken</t>
   </si>
   <si>
@@ -394,15 +328,9 @@
     <t>■ BIZEPS</t>
   </si>
   <si>
-    <t>Kabel Curls, neutral</t>
-  </si>
-  <si>
     <t>Unterarme</t>
   </si>
   <si>
-    <t>Kabel Curls, Untergriff</t>
-  </si>
-  <si>
     <t>Kabel Schrägbank Spider Curls</t>
   </si>
   <si>
@@ -418,30 +346,15 @@
     <t>KH Curls, alternierend, rotierend</t>
   </si>
   <si>
-    <t>KH Curls, Untergriff</t>
-  </si>
-  <si>
     <t>KH Hammercurls</t>
   </si>
   <si>
-    <t>KH Konzentrationscurls, Untergriff</t>
-  </si>
-  <si>
     <t>KH Schrägbank Spider Curls</t>
   </si>
   <si>
-    <t>KH Schrägbankcurls, neutral</t>
-  </si>
-  <si>
-    <t>KH Schrägbankcurls, Untergriff</t>
-  </si>
-  <si>
     <t>KH Scott Curls</t>
   </si>
   <si>
-    <t>LH Curls, Untergriff</t>
-  </si>
-  <si>
     <t>LH Schrägbank Spider Curls</t>
   </si>
   <si>
@@ -451,15 +364,9 @@
     <t>PlateLoaded Scott Curls, Maschine</t>
   </si>
   <si>
-    <t>Steck Curls, Untergriff</t>
-  </si>
-  <si>
     <t>Steck Scott Curls, Maschine</t>
   </si>
   <si>
-    <t>SZ Curls, Untergriff</t>
-  </si>
-  <si>
     <t>SZ Schrägbank Spider Curls</t>
   </si>
   <si>
@@ -487,21 +394,9 @@
     <t>—</t>
   </si>
   <si>
-    <t>Kabel Trizepsstrecken, Obergriff</t>
-  </si>
-  <si>
-    <t>Kabel Trizepsstrecken, Überkopf</t>
-  </si>
-  <si>
-    <t>Kabel Trizepsstrecken, Untergriff</t>
-  </si>
-  <si>
     <t>KH Kickbacks</t>
   </si>
   <si>
-    <t>KH Trizepsstrecken, liegend, neutral</t>
-  </si>
-  <si>
     <t>KH Trizepsstrecken, Überkopf</t>
   </si>
   <si>
@@ -817,9 +712,6 @@
     <t>SZ JM Press</t>
   </si>
   <si>
-    <t>Kabel Trizepsstrecken, neutral</t>
-  </si>
-  <si>
     <t>LH Seal Rows</t>
   </si>
   <si>
@@ -838,10 +730,79 @@
     <t>LH Back Extensions</t>
   </si>
   <si>
-    <t>Multipresse Rudern, schulterbreit, Obergriff</t>
-  </si>
-  <si>
     <t>KH Rudern, Obergriff</t>
+  </si>
+  <si>
+    <t>Kabel Rudern, eng, Hammergriff</t>
+  </si>
+  <si>
+    <t>KH Rudern</t>
+  </si>
+  <si>
+    <t>Klimmzug, eng, Hammergriff</t>
+  </si>
+  <si>
+    <t>Klimmzug, Obergriff</t>
+  </si>
+  <si>
+    <t>Klimmzug, Untergriff</t>
+  </si>
+  <si>
+    <t>Latziehen in den Nacken</t>
+  </si>
+  <si>
+    <t>Latziehen zur Brust</t>
+  </si>
+  <si>
+    <t>LH Rudern, Obergriff</t>
+  </si>
+  <si>
+    <t>LH Rudern, Untergriff</t>
+  </si>
+  <si>
+    <t>LH T-Bar Rudern</t>
+  </si>
+  <si>
+    <t>Multipresse Rudern, Untergriff</t>
+  </si>
+  <si>
+    <t>Multipresse Rudern, Obergriff</t>
+  </si>
+  <si>
+    <t>Steck Rudern, Obergriff</t>
+  </si>
+  <si>
+    <t>Steck Rudern, Untergriff</t>
+  </si>
+  <si>
+    <t>PlateLoaded Rudern</t>
+  </si>
+  <si>
+    <t>Kabel Curls</t>
+  </si>
+  <si>
+    <t>KH Curls</t>
+  </si>
+  <si>
+    <t>KH Konzentrationscurls</t>
+  </si>
+  <si>
+    <t>KH Schrägbankcurls</t>
+  </si>
+  <si>
+    <t>LH Curls</t>
+  </si>
+  <si>
+    <t>Steck Curls</t>
+  </si>
+  <si>
+    <t>SZ Curls</t>
+  </si>
+  <si>
+    <t>Kabel Trizepsstrecken</t>
+  </si>
+  <si>
+    <t>KH Trizepsstrecken, liegend</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1001"/>
+  <dimension ref="A1:D988"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1446,10 +1407,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1460,10 +1421,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1488,10 +1449,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1502,21 +1463,21 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>8</v>
@@ -1530,7 +1491,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>8</v>
@@ -1592,7 +1553,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
@@ -1642,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>8</v>
@@ -1673,7 +1634,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -1684,7 +1645,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>8</v>
@@ -1698,10 +1659,10 @@
         <v>6</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -1740,10 +1701,10 @@
         <v>6</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -1754,7 +1715,7 @@
         <v>6</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>8</v>
@@ -1768,71 +1729,71 @@
         <v>6</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+      <c r="D34" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="D35" s="6" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="36" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>45</v>
+        <v>239</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>8</v>
@@ -1840,27 +1801,27 @@
     </row>
     <row r="37" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>47</v>
+        <v>240</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>48</v>
+        <v>241</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>8</v>
@@ -1868,27 +1829,27 @@
     </row>
     <row r="39" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>49</v>
+        <v>242</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="33" t="s">
-        <v>51</v>
+      <c r="A40" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>8</v>
@@ -1896,119 +1857,119 @@
     </row>
     <row r="41" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="33" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="33" t="s">
-        <v>54</v>
+      <c r="A42" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="33" t="s">
-        <v>55</v>
+      <c r="A43" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="33" t="s">
+      <c r="B47" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="49" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>12</v>
@@ -2016,41 +1977,41 @@
     </row>
     <row r="50" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="34" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>67</v>
+        <v>244</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>8</v>
@@ -2058,41 +2019,41 @@
     </row>
     <row r="53" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="34" t="s">
-        <v>70</v>
+      <c r="A54" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="34" t="s">
-        <v>71</v>
+      <c r="A55" s="7" t="s">
+        <v>230</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>8</v>
@@ -2100,13 +2061,13 @@
     </row>
     <row r="56" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>72</v>
+        <v>247</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>8</v>
@@ -2114,41 +2075,41 @@
     </row>
     <row r="57" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>73</v>
+        <v>248</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="34" t="s">
-        <v>74</v>
+      <c r="A58" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="34" t="s">
-        <v>75</v>
+      <c r="A59" s="7" t="s">
+        <v>251</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>8</v>
@@ -2156,13 +2117,13 @@
     </row>
     <row r="60" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>266</v>
+        <v>62</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>8</v>
@@ -2170,13 +2131,13 @@
     </row>
     <row r="61" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>76</v>
+        <v>232</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>8</v>
@@ -2184,41 +2145,41 @@
     </row>
     <row r="62" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>272</v>
+        <v>63</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="34" t="s">
-        <v>78</v>
+      <c r="A64" s="7" t="s">
+        <v>249</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>8</v>
@@ -2226,13 +2187,13 @@
     </row>
     <row r="65" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>8</v>
@@ -2240,147 +2201,147 @@
     </row>
     <row r="66" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>268</v>
+        <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C66" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D66" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
     </row>
     <row r="68" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D68" s="8" t="s">
+      <c r="A68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C69" s="7" t="s">
+      <c r="A69" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D69" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C71" s="7" t="s">
+      <c r="D71" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D71" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
+      <c r="D73" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="74" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C74" s="9" t="s">
-        <v>88</v>
+      <c r="C74" s="35" t="s">
+        <v>70</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C75" s="9" t="s">
-        <v>88</v>
+      <c r="C75" s="35" t="s">
+        <v>70</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C76" s="9" t="s">
-        <v>91</v>
+      <c r="C76" s="35" t="s">
+        <v>70</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>8</v>
@@ -2388,147 +2349,145 @@
     </row>
     <row r="77" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C77" s="35" t="s">
-        <v>91</v>
+      <c r="C77" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" s="9" t="s">
+      <c r="A78" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+    </row>
+    <row r="79" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C82" s="13"/>
+      <c r="D82" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C85" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D78" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C83" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C84" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B85" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D85" s="10" t="s">
-        <v>12</v>
+      <c r="D85" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
+      <c r="A86" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="87" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="11" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B87" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C87" s="11" t="s">
         <v>88</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>52</v>
       </c>
       <c r="D87" s="12" t="s">
         <v>8</v>
@@ -2536,53 +2495,55 @@
     </row>
     <row r="88" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B88" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C88" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C88" s="11" t="s">
-        <v>104</v>
-      </c>
       <c r="D88" s="12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B89" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C90" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B90" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C90" s="13"/>
-      <c r="D90" s="14" t="s">
-        <v>12</v>
+      <c r="D90" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D91" s="12" t="s">
         <v>12</v>
@@ -2590,253 +2551,253 @@
     </row>
     <row r="92" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C92" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+    </row>
+    <row r="94" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C94" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D92" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C94" s="11" t="s">
+      <c r="D94" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C95" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D94" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>8</v>
+      <c r="D95" s="14" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>8</v>
+      <c r="A96" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B97" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D97" s="12" t="s">
+      <c r="A97" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D97" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>8</v>
+      <c r="A98" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C99" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D99" s="12" t="s">
+      <c r="A99" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D99" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B100" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C100" s="11" t="s">
+      <c r="A100" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C100" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D100" s="12" t="s">
-        <v>8</v>
+      <c r="D100" s="14" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
     </row>
     <row r="102" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B102" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C102" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D102" s="14" t="s">
+      <c r="A102" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B102" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C102" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D102" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="13" t="s">
+      <c r="A103" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B103" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C103" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B104" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C104" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D104" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B106" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C106" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="D106" s="37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C107" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="B103" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C103" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D103" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B104" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C104" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D104" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="B105" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C105" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D105" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="B106" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C106" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D106" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B107" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C107" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D107" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B108" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C108" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D108" s="14" t="s">
+      <c r="B108" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C108" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D108" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
+      <c r="A109" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B109" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C109" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D109" s="16" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="110" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="15" t="s">
-        <v>124</v>
+        <v>254</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D110" s="16" t="s">
         <v>12</v>
@@ -2844,13 +2805,13 @@
     </row>
     <row r="111" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="15" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D111" s="16" t="s">
         <v>12</v>
@@ -2858,13 +2819,13 @@
     </row>
     <row r="112" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="15" t="s">
-        <v>127</v>
+        <v>255</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D112" s="16" t="s">
         <v>12</v>
@@ -2872,13 +2833,13 @@
     </row>
     <row r="113" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="15" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D113" s="16" t="s">
         <v>12</v>
@@ -2886,41 +2847,41 @@
     </row>
     <row r="114" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="15" t="s">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D114" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="B115" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="C115" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="D115" s="37" t="s">
+      <c r="A115" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B115" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C115" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D115" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="15" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D116" s="16" t="s">
         <v>12</v>
@@ -2928,13 +2889,13 @@
     </row>
     <row r="117" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="15" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D117" s="16" t="s">
         <v>12</v>
@@ -2942,13 +2903,13 @@
     </row>
     <row r="118" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="15" t="s">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D118" s="16" t="s">
         <v>12</v>
@@ -2956,13 +2917,13 @@
     </row>
     <row r="119" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="15" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D119" s="16" t="s">
         <v>12</v>
@@ -2970,13 +2931,13 @@
     </row>
     <row r="120" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="15" t="s">
-        <v>135</v>
+        <v>258</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D120" s="16" t="s">
         <v>12</v>
@@ -2984,13 +2945,13 @@
     </row>
     <row r="121" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="15" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D121" s="16" t="s">
         <v>12</v>
@@ -2998,175 +2959,175 @@
     </row>
     <row r="122" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C122" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D122" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+    </row>
+    <row r="124" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B124" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C124" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D124" s="18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B125" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C125" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D125" s="18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B126" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C126" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D126" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="B127" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C127" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D127" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="B128" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C128" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D128" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="B129" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C129" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D129" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="D122" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B123" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C123" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D123" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="B124" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C124" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D124" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="B125" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C125" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D125" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B126" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C126" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D126" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="B127" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C127" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D127" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="B128" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C128" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D128" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="B129" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C129" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D129" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B130" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C130" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D130" s="16" t="s">
+      <c r="B130" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C130" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D130" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="B131" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C131" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D131" s="16" t="s">
+      <c r="A131" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B131" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C131" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D131" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="B132" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C132" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D132" s="16" t="s">
+      <c r="A132" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B132" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C132" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D132" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
+      <c r="A133" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="B133" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C133" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D133" s="18" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="134" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="17" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="D134" s="18" t="s">
         <v>8</v>
@@ -3174,27 +3135,27 @@
     </row>
     <row r="135" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="17" t="s">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="17" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="D136" s="18" t="s">
         <v>12</v>
@@ -3202,391 +3163,391 @@
     </row>
     <row r="137" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="17" t="s">
-        <v>265</v>
+        <v>131</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="D137" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="B138" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C138" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D138" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="B139" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C139" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D139" s="18" t="s">
+      <c r="A138" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+    </row>
+    <row r="139" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D139" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B140" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C140" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D140" s="18" t="s">
+      <c r="A140" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C140" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D140" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="B141" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C141" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D141" s="18" t="s">
+      <c r="A141" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D141" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B142" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C142" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D142" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="B143" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C143" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D143" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B144" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C144" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D144" s="18" t="s">
+      <c r="A142" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C142" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D142" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D143" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="B144" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C144" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D144" s="39" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="B145" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C145" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D145" s="18" t="s">
+      <c r="A145" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D145" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="B146" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C146" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="D146" s="18" t="s">
-        <v>8</v>
+      <c r="A146" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D146" s="20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="B147" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C147" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="D147" s="18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="B148" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C148" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D148" s="18" t="s">
+      <c r="A147" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B147" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D147" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B148" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C148" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D148" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="B149" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C149" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D149" s="18" t="s">
+      <c r="A149" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C149" s="19"/>
+      <c r="D149" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="B150" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C150" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D150" s="18" t="s">
+      <c r="A150" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C150" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D150" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
     </row>
-    <row r="152" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="B152" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C152" s="19" t="s">
+    <row r="152" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B152" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C152" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D152" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B153" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C153" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D153" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B154" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C154" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D154" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="B155" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C155" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D155" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B156" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C156" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D156" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B157" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C157" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D157" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B158" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C158" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D158" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B159" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C159" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D159" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="D152" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="B153" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C153" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D153" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="B154" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C154" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="D154" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="B155" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C155" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="D155" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="B156" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C156" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="D156" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="B157" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="C157" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D157" s="39" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B158" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C158" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D158" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="B159" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C159" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="D159" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B160" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C160" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="D160" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="B161" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C161" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="D161" s="20" t="s">
-        <v>12</v>
+      <c r="B160" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C160" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D160" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="B161" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C161" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D161" s="22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="B162" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C162" s="19"/>
-      <c r="D162" s="20" t="s">
-        <v>12</v>
+      <c r="A162" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B162" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C162" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D162" s="22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="B163" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C163" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D163" s="20" t="s">
-        <v>12</v>
+      <c r="A163" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B163" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C163" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D163" s="22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B164" s="2"/>
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
+      <c r="A164" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="B164" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C164" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D164" s="22" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="165" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="21" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>8</v>
@@ -3594,27 +3555,27 @@
     </row>
     <row r="166" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="21" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="D166" s="22" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="21" t="s">
-        <v>259</v>
+        <v>160</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="D167" s="22" t="s">
         <v>8</v>
@@ -3622,13 +3583,13 @@
     </row>
     <row r="168" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="21" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="D168" s="22" t="s">
         <v>8</v>
@@ -3636,13 +3597,13 @@
     </row>
     <row r="169" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="21" t="s">
-        <v>261</v>
+        <v>161</v>
       </c>
       <c r="B169" s="21" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="D169" s="22" t="s">
         <v>8</v>
@@ -3650,916 +3611,747 @@
     </row>
     <row r="170" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="21" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="B170" s="21" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="D170" s="22" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="B171" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C171" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="D171" s="22" t="s">
-        <v>8</v>
-      </c>
+      <c r="A171" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
     </row>
     <row r="172" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="B172" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C172" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D172" s="22" t="s">
+      <c r="A172" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B172" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C172" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D172" s="24" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="B173" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C173" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D173" s="22" t="s">
+      <c r="A173" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="B173" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C173" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D173" s="24" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="B174" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C174" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D174" s="22" t="s">
+      <c r="A174" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B174" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C174" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D174" s="24" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="B175" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C175" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D175" s="22" t="s">
+      <c r="A175" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B175" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C175" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D175" s="24" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="B176" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C176" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D176" s="22" t="s">
+      <c r="A176" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B176" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C176" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D176" s="24" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="B177" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C177" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D177" s="22" t="s">
+      <c r="A177" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="B177" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C177" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D177" s="24" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="B178" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C178" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D178" s="22" t="s">
+      <c r="A178" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="B178" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C178" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D178" s="24" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B179" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C179" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D179" s="22" t="s">
+      <c r="A179" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="B179" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C179" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D179" s="24" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="B180" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C180" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D180" s="22" t="s">
-        <v>8</v>
+      <c r="A180" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="B180" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C180" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D180" s="24" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="21" t="s">
-        <v>257</v>
-      </c>
-      <c r="B181" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C181" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D181" s="22" t="s">
-        <v>8</v>
+      <c r="A181" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="B181" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C181" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D181" s="24" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="B182" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C182" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D182" s="22" t="s">
-        <v>8</v>
+      <c r="A182" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="B182" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C182" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D182" s="24" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="B183" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C183" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D183" s="22" t="s">
+      <c r="A183" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="B183" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C183" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D183" s="24" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B184" s="2"/>
-      <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
+      <c r="A184" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B184" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C184" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D184" s="24" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="185" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="B185" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C185" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D185" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+    </row>
+    <row r="187" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="B187" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C187" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D187" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="B188" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C188" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D188" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="B189" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C189" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D189" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="B190" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C190" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D190" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="B191" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C191" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D191" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="B192" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C192" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="D192" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="B193" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C193" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="D193" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B194" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C194" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D194" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="B195" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C195" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D195" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="B196" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C196" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D196" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="B197" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C197" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D197" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+    </row>
+    <row r="199" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="B199" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C199" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D199" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B200" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C200" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D200" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="B201" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C201" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D201" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B202" s="2"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
+    </row>
+    <row r="203" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="B203" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C203" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D203" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="B204" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C204" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D204" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B205" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C205" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D205" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="B185" s="23" t="s">
+      <c r="B206" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C206" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D206" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="C185" s="23" t="s">
+      <c r="B207" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C207" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D207" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="D185" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="23" t="s">
+      <c r="B208" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C208" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D208" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="B186" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C186" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="D186" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="23" t="s">
+      <c r="B209" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C209" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D209" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="B210" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C210" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D210" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="B187" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C187" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="D187" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="23" t="s">
+      <c r="B211" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C211" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D211" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="B188" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C188" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="D188" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="23" t="s">
+      <c r="B212" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C212" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D212" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B189" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C189" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="D189" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="B190" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C190" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="D190" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="23" t="s">
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
+    </row>
+    <row r="214" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="B214" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="B191" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C191" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="D191" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="23" t="s">
+      <c r="C214" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D214" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="B215" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C215" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D215" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="B216" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C216" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D216" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="B217" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C217" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D217" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="B218" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C218" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D218" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="B219" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C219" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D219" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" s="31" t="s">
+        <v>211</v>
+      </c>
+      <c r="B220" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C220" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D220" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="B192" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C192" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="D192" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="23" t="s">
+      <c r="B221" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C221" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D221" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="B193" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C193" s="23" t="s">
+      <c r="B222" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C222" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D222" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="D193" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="B194" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C194" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="D194" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="B195" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C195" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="D195" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="B196" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C196" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="D196" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="B197" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C197" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="D197" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="B198" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C198" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="D198" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B199" s="2"/>
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
-    </row>
-    <row r="200" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="B200" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C200" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="D200" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="B201" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C201" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="D201" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="25" t="s">
-        <v>270</v>
-      </c>
-      <c r="B202" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C202" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="D202" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="25" t="s">
-        <v>271</v>
-      </c>
-      <c r="B203" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C203" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="D203" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="B204" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C204" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="D204" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="B205" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C205" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="D205" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="B206" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C206" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="D206" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="B207" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C207" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="D207" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="B208" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C208" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D208" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="B209" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C209" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="D209" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B210" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C210" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D210" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B211" s="2"/>
-      <c r="C211" s="2"/>
-      <c r="D211" s="2"/>
-    </row>
-    <row r="212" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="B212" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="C212" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D212" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="B213" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="C213" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D213" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="B214" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="C214" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D214" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B215" s="2"/>
-      <c r="C215" s="2"/>
-      <c r="D215" s="2"/>
-    </row>
-    <row r="216" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="B216" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C216" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D216" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="29" t="s">
-        <v>232</v>
-      </c>
-      <c r="B217" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C217" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D217" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="29" t="s">
-        <v>233</v>
-      </c>
-      <c r="B218" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C218" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D218" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A219" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="B219" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C219" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D219" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="B220" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C220" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D220" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="B221" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C221" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D221" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="B222" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C222" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D222" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A223" s="29" t="s">
-        <v>256</v>
-      </c>
-      <c r="B223" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C223" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D223" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="29" t="s">
-        <v>238</v>
-      </c>
-      <c r="B224" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C224" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D224" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A225" s="29" t="s">
-        <v>239</v>
-      </c>
-      <c r="B225" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C225" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D225" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B226" s="2"/>
-      <c r="C226" s="2"/>
-      <c r="D226" s="2"/>
-    </row>
-    <row r="227" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A227" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="B227" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C227" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D227" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A228" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="B228" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C228" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D228" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="B229" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C229" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D229" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="B230" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C230" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D230" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="31" t="s">
-        <v>250</v>
-      </c>
-      <c r="B231" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C231" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D231" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A232" s="31" t="s">
-        <v>251</v>
-      </c>
-      <c r="B232" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C232" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D232" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A233" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="B233" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C233" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D233" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A234" s="31" t="s">
-        <v>242</v>
-      </c>
-      <c r="B234" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C234" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D234" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="B235" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C235" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D235" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="B236" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C236" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D236" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B223" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C223" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D223" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="241" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="242" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="243" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5308,19 +5100,6 @@
     <row r="986" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="987" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="988" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1ED706-312F-8542-B21F-89C23584ADC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11C3108-6C9E-A143-8966-802E35D7D2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Übungsliste" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="262">
   <si>
     <t>Übung</t>
   </si>
@@ -803,6 +803,9 @@
   </si>
   <si>
     <t>KH Trizepsstrecken, liegend</t>
+  </si>
+  <si>
+    <t>Comp, Iso</t>
   </si>
 </sst>
 </file>
@@ -1768,7 +1771,7 @@
         <v>6</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>12</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -1894,7 +1897,7 @@
         <v>6</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>12</v>
+        <v>261</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">

--- a/Übungskatalog.xlsx
+++ b/Übungskatalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flrn/Projects/blast-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11C3108-6C9E-A143-8966-802E35D7D2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060FF7FC-17B5-2448-A668-D4722E06F5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="263">
   <si>
     <t>Übung</t>
   </si>
@@ -805,7 +805,10 @@
     <t>KH Trizepsstrecken, liegend</t>
   </si>
   <si>
-    <t>Comp, Iso</t>
+    <t>Kabel Überzüge, weit</t>
+  </si>
+  <si>
+    <t>LH Überzüge, weit</t>
   </si>
 </sst>
 </file>
@@ -1300,7 +1303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D988"/>
+  <dimension ref="A1:D990"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1771,18 +1774,18 @@
         <v>6</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>261</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>8</v>
@@ -1790,13 +1793,13 @@
     </row>
     <row r="36" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>8</v>
@@ -1804,13 +1807,13 @@
     </row>
     <row r="37" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>8</v>
@@ -1818,13 +1821,13 @@
     </row>
     <row r="38" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>8</v>
@@ -1832,13 +1835,13 @@
     </row>
     <row r="39" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>8</v>
@@ -1846,35 +1849,35 @@
     </row>
     <row r="40" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="33" t="s">
-        <v>47</v>
+      <c r="A41" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>231</v>
+      <c r="A42" s="33" t="s">
+        <v>47</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>14</v>
@@ -1888,77 +1891,77 @@
     </row>
     <row r="43" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
+      <c r="D44" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="7" t="s">
-        <v>236</v>
+      <c r="A48" s="34" t="s">
+        <v>54</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>8</v>
@@ -1966,7 +1969,7 @@
     </row>
     <row r="49" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>52</v>
@@ -1979,70 +1982,70 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="34" t="s">
-        <v>59</v>
+      <c r="A50" s="7" t="s">
+        <v>236</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>244</v>
+        <v>58</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="7" t="s">
-        <v>245</v>
+      <c r="A52" s="34" t="s">
+        <v>59</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>60</v>
+        <v>244</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>8</v>
@@ -2050,27 +2053,27 @@
     </row>
     <row r="55" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>8</v>
@@ -2078,7 +2081,7 @@
     </row>
     <row r="57" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>52</v>
@@ -2092,21 +2095,21 @@
     </row>
     <row r="58" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>61</v>
+        <v>247</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>52</v>
@@ -2120,21 +2123,21 @@
     </row>
     <row r="60" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>52</v>
@@ -2148,141 +2151,141 @@
     </row>
     <row r="62" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>64</v>
+        <v>232</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>249</v>
+        <v>63</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>65</v>
+        <v>249</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C66" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D66" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="2" t="s">
+      <c r="D68" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-    </row>
-    <row r="68" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>8</v>
-      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
     </row>
     <row r="70" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C70" s="35" t="s">
-        <v>70</v>
+      <c r="C70" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>11</v>
@@ -2296,7 +2299,7 @@
     </row>
     <row r="73" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>11</v>
@@ -2310,7 +2313,7 @@
     </row>
     <row r="74" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>11</v>
@@ -2324,21 +2327,21 @@
     </row>
     <row r="75" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C75" s="35" t="s">
-        <v>70</v>
+      <c r="C75" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>11</v>
@@ -2352,57 +2355,57 @@
     </row>
     <row r="77" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D77" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="2" t="s">
+      <c r="D79" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-    </row>
-    <row r="79" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>12</v>
-      </c>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
     </row>
     <row r="81" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>68</v>
@@ -2415,62 +2418,62 @@
       </c>
     </row>
     <row r="82" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B82" s="13" t="s">
+      <c r="A82" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C82" s="13"/>
-      <c r="D82" s="14" t="s">
+      <c r="C82" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>68</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B84" s="11" t="s">
+      <c r="A84" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C84" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>8</v>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>68</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>68</v>
@@ -2484,7 +2487,7 @@
     </row>
     <row r="87" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>68</v>
@@ -2498,13 +2501,13 @@
     </row>
     <row r="88" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>68</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>8</v>
@@ -2512,21 +2515,21 @@
     </row>
     <row r="89" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>68</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>68</v>
@@ -2540,7 +2543,7 @@
     </row>
     <row r="91" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>68</v>
@@ -2554,57 +2557,57 @@
     </row>
     <row r="92" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>68</v>
       </c>
       <c r="C92" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C94" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D92" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="2" t="s">
+      <c r="D94" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-    </row>
-    <row r="94" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B94" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C94" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D94" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="B95" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C95" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>12</v>
-      </c>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
     </row>
     <row r="96" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B96" s="13" t="s">
         <v>53</v>
@@ -2618,7 +2621,7 @@
     </row>
     <row r="97" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B97" s="13" t="s">
         <v>53</v>
@@ -2632,7 +2635,7 @@
     </row>
     <row r="98" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="13" t="s">
-        <v>220</v>
+        <v>98</v>
       </c>
       <c r="B98" s="13" t="s">
         <v>53</v>
@@ -2646,7 +2649,7 @@
     </row>
     <row r="99" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="13" t="s">
-        <v>99</v>
+        <v>219</v>
       </c>
       <c r="B99" s="13" t="s">
         <v>53</v>
@@ -2660,7 +2663,7 @@
     </row>
     <row r="100" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="13" t="s">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="B100" s="13" t="s">
         <v>53</v>
@@ -2673,44 +2676,44 @@
       </c>
     </row>
     <row r="101" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D102" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-    </row>
-    <row r="102" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="B102" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C102" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D102" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B103" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C103" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D103" s="16" t="s">
-        <v>12</v>
-      </c>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
     </row>
     <row r="104" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="15" t="s">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="B104" s="15" t="s">
         <v>48</v>
@@ -2724,7 +2727,7 @@
     </row>
     <row r="105" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B105" s="15" t="s">
         <v>48</v>
@@ -2737,22 +2740,22 @@
       </c>
     </row>
     <row r="106" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="B106" s="36" t="s">
+      <c r="A106" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B106" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C106" s="36" t="s">
+      <c r="C106" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="37" t="s">
+      <c r="D106" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B107" s="15" t="s">
         <v>48</v>
@@ -2765,22 +2768,22 @@
       </c>
     </row>
     <row r="108" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="B108" s="15" t="s">
+      <c r="A108" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B108" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="C108" s="15" t="s">
+      <c r="C108" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="D108" s="16" t="s">
+      <c r="D108" s="37" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B109" s="15" t="s">
         <v>48</v>
@@ -2794,7 +2797,7 @@
     </row>
     <row r="110" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B110" s="15" t="s">
         <v>48</v>
@@ -2808,7 +2811,7 @@
     </row>
     <row r="111" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B111" s="15" t="s">
         <v>48</v>
@@ -2822,7 +2825,7 @@
     </row>
     <row r="112" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B112" s="15" t="s">
         <v>48</v>
@@ -2836,7 +2839,7 @@
     </row>
     <row r="113" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B113" s="15" t="s">
         <v>48</v>
@@ -2850,7 +2853,7 @@
     </row>
     <row r="114" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B114" s="15" t="s">
         <v>48</v>
@@ -2864,7 +2867,7 @@
     </row>
     <row r="115" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B115" s="15" t="s">
         <v>48</v>
@@ -2878,7 +2881,7 @@
     </row>
     <row r="116" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="15" t="s">
-        <v>112</v>
+        <v>256</v>
       </c>
       <c r="B116" s="15" t="s">
         <v>48</v>
@@ -2892,7 +2895,7 @@
     </row>
     <row r="117" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B117" s="15" t="s">
         <v>48</v>
@@ -2906,7 +2909,7 @@
     </row>
     <row r="118" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="15" t="s">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="B118" s="15" t="s">
         <v>48</v>
@@ -2920,7 +2923,7 @@
     </row>
     <row r="119" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B119" s="15" t="s">
         <v>48</v>
@@ -2934,7 +2937,7 @@
     </row>
     <row r="120" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B120" s="15" t="s">
         <v>48</v>
@@ -2948,7 +2951,7 @@
     </row>
     <row r="121" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B121" s="15" t="s">
         <v>48</v>
@@ -2962,7 +2965,7 @@
     </row>
     <row r="122" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
-        <v>116</v>
+        <v>258</v>
       </c>
       <c r="B122" s="15" t="s">
         <v>48</v>
@@ -2975,72 +2978,72 @@
       </c>
     </row>
     <row r="123" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B123" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C123" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D123" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B124" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C124" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D124" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
-    </row>
-    <row r="124" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="B124" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C124" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="D124" s="18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="B125" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C125" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="D125" s="18" t="s">
-        <v>8</v>
-      </c>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
     </row>
     <row r="126" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="17" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B126" s="17" t="s">
         <v>119</v>
       </c>
       <c r="C126" s="17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D126" s="18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="17" t="s">
-        <v>259</v>
+        <v>121</v>
       </c>
       <c r="B127" s="17" t="s">
         <v>119</v>
       </c>
       <c r="C127" s="17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D127" s="18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B128" s="17" t="s">
         <v>119</v>
@@ -3054,7 +3057,7 @@
     </row>
     <row r="129" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B129" s="17" t="s">
         <v>119</v>
@@ -3068,7 +3071,7 @@
     </row>
     <row r="130" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B130" s="17" t="s">
         <v>119</v>
@@ -3082,7 +3085,7 @@
     </row>
     <row r="131" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="17" t="s">
-        <v>126</v>
+        <v>260</v>
       </c>
       <c r="B131" s="17" t="s">
         <v>119</v>
@@ -3096,7 +3099,7 @@
     </row>
     <row r="132" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B132" s="17" t="s">
         <v>119</v>
@@ -3110,63 +3113,63 @@
     </row>
     <row r="133" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B133" s="17" t="s">
         <v>119</v>
       </c>
       <c r="C133" s="17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B134" s="17" t="s">
         <v>119</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D134" s="18" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="17" t="s">
-        <v>229</v>
+        <v>128</v>
       </c>
       <c r="B135" s="17" t="s">
         <v>119</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B136" s="17" t="s">
         <v>119</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D136" s="18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="17" t="s">
-        <v>131</v>
+        <v>229</v>
       </c>
       <c r="B137" s="17" t="s">
         <v>119</v>
@@ -3179,44 +3182,44 @@
       </c>
     </row>
     <row r="138" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B138" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C138" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D138" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B139" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C139" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D139" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B138" s="2"/>
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
-    </row>
-    <row r="139" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="19" t="s">
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+    </row>
+    <row r="141" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="19" t="s">
         <v>133</v>
-      </c>
-      <c r="B139" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="C139" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D139" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="B140" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="C140" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D140" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="19" t="s">
-        <v>135</v>
       </c>
       <c r="B141" s="19" t="s">
         <v>102</v>
@@ -3230,21 +3233,21 @@
     </row>
     <row r="142" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B142" s="19" t="s">
         <v>102</v>
       </c>
       <c r="C142" s="19" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="D142" s="20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B143" s="19" t="s">
         <v>102</v>
@@ -3256,65 +3259,65 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="B144" s="38" t="s">
+    <row r="144" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B144" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C144" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D144" s="39" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C144" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D144" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B145" s="19" t="s">
         <v>102</v>
       </c>
       <c r="C145" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D145" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="B146" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C146" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="D145" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="B146" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="C146" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D146" s="20" t="s">
+      <c r="D146" s="39" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B147" s="19" t="s">
         <v>102</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="D147" s="20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B148" s="19" t="s">
         <v>102</v>
@@ -3328,75 +3331,75 @@
     </row>
     <row r="149" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B149" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C149" s="19"/>
+      <c r="C149" s="19" t="s">
+        <v>123</v>
+      </c>
       <c r="D149" s="20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B150" s="19" t="s">
         <v>102</v>
       </c>
       <c r="C150" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D150" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C151" s="19"/>
+      <c r="D151" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C152" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D150" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="2" t="s">
+      <c r="D152" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B151" s="2"/>
-      <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
-    </row>
-    <row r="152" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B152" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="C152" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="D152" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="B153" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="C153" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="D153" s="22" t="s">
-        <v>8</v>
-      </c>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
     </row>
     <row r="154" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="21" t="s">
-        <v>224</v>
+        <v>146</v>
       </c>
       <c r="B154" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C154" s="21" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D154" s="22" t="s">
         <v>8</v>
@@ -3404,13 +3407,13 @@
     </row>
     <row r="155" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="21" t="s">
-        <v>225</v>
+        <v>149</v>
       </c>
       <c r="B155" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C155" s="21" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D155" s="22" t="s">
         <v>8</v>
@@ -3418,7 +3421,7 @@
     </row>
     <row r="156" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B156" s="21" t="s">
         <v>147</v>
@@ -3432,13 +3435,13 @@
     </row>
     <row r="157" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="21" t="s">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="B157" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C157" s="21" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D157" s="22" t="s">
         <v>8</v>
@@ -3446,13 +3449,13 @@
     </row>
     <row r="158" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="21" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="B158" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D158" s="22" t="s">
         <v>8</v>
@@ -3460,13 +3463,13 @@
     </row>
     <row r="159" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B159" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C159" s="21" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D159" s="22" t="s">
         <v>8</v>
@@ -3474,13 +3477,13 @@
     </row>
     <row r="160" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="21" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B160" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C160" s="21" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D160" s="22" t="s">
         <v>8</v>
@@ -3488,13 +3491,13 @@
     </row>
     <row r="161" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="21" t="s">
-        <v>227</v>
+        <v>152</v>
       </c>
       <c r="B161" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C161" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D161" s="22" t="s">
         <v>8</v>
@@ -3502,13 +3505,13 @@
     </row>
     <row r="162" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="21" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B162" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D162" s="22" t="s">
         <v>8</v>
@@ -3516,7 +3519,7 @@
     </row>
     <row r="163" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="21" t="s">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="B163" s="21" t="s">
         <v>147</v>
@@ -3530,13 +3533,13 @@
     </row>
     <row r="164" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="21" t="s">
-        <v>223</v>
+        <v>156</v>
       </c>
       <c r="B164" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D164" s="22" t="s">
         <v>8</v>
@@ -3544,7 +3547,7 @@
     </row>
     <row r="165" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B165" s="21" t="s">
         <v>147</v>
@@ -3558,21 +3561,21 @@
     </row>
     <row r="166" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="21" t="s">
-        <v>159</v>
+        <v>223</v>
       </c>
       <c r="B166" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="D166" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B167" s="21" t="s">
         <v>147</v>
@@ -3586,21 +3589,21 @@
     </row>
     <row r="168" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="21" t="s">
-        <v>222</v>
+        <v>159</v>
       </c>
       <c r="B168" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B169" s="21" t="s">
         <v>147</v>
@@ -3614,57 +3617,57 @@
     </row>
     <row r="170" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="21" t="s">
-        <v>162</v>
+        <v>222</v>
       </c>
       <c r="B170" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C170" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D170" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B171" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C171" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D171" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B172" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C172" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="D170" s="22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="2" t="s">
+      <c r="D172" s="22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B171" s="2"/>
-      <c r="C171" s="2"/>
-      <c r="D171" s="2"/>
-    </row>
-    <row r="172" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="B172" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="C172" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="D172" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="B173" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="C173" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="D173" s="24" t="s">
-        <v>8</v>
-      </c>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
     </row>
     <row r="174" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="23" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B174" s="23" t="s">
         <v>165</v>
@@ -3678,7 +3681,7 @@
     </row>
     <row r="175" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B175" s="23" t="s">
         <v>165</v>
@@ -3692,13 +3695,13 @@
     </row>
     <row r="176" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="23" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B176" s="23" t="s">
         <v>165</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D176" s="24" t="s">
         <v>8</v>
@@ -3706,7 +3709,7 @@
     </row>
     <row r="177" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="23" t="s">
-        <v>233</v>
+        <v>169</v>
       </c>
       <c r="B177" s="23" t="s">
         <v>165</v>
@@ -3720,7 +3723,7 @@
     </row>
     <row r="178" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B178" s="23" t="s">
         <v>165</v>
@@ -3734,7 +3737,7 @@
     </row>
     <row r="179" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="23" t="s">
-        <v>172</v>
+        <v>233</v>
       </c>
       <c r="B179" s="23" t="s">
         <v>165</v>
@@ -3743,32 +3746,32 @@
         <v>153</v>
       </c>
       <c r="D179" s="24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B180" s="23" t="s">
         <v>165</v>
       </c>
       <c r="C180" s="23" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D180" s="24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B181" s="23" t="s">
         <v>165</v>
       </c>
       <c r="C181" s="23" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D181" s="24" t="s">
         <v>12</v>
@@ -3776,7 +3779,7 @@
     </row>
     <row r="182" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B182" s="23" t="s">
         <v>165</v>
@@ -3790,7 +3793,7 @@
     </row>
     <row r="183" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B183" s="23" t="s">
         <v>165</v>
@@ -3804,7 +3807,7 @@
     </row>
     <row r="184" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B184" s="23" t="s">
         <v>165</v>
@@ -3818,7 +3821,7 @@
     </row>
     <row r="185" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="23" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B185" s="23" t="s">
         <v>165</v>
@@ -3831,44 +3834,44 @@
       </c>
     </row>
     <row r="186" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="2" t="s">
+      <c r="A186" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B186" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C186" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D186" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="B187" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C187" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D187" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B186" s="2"/>
-      <c r="C186" s="2"/>
-      <c r="D186" s="2"/>
-    </row>
-    <row r="187" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="B187" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="C187" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="D187" s="26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="B188" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="C188" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="D188" s="26" t="s">
-        <v>12</v>
-      </c>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
     </row>
     <row r="189" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="25" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="B189" s="25" t="s">
         <v>153</v>
@@ -3882,7 +3885,7 @@
     </row>
     <row r="190" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="25" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B190" s="25" t="s">
         <v>153</v>
@@ -3896,7 +3899,7 @@
     </row>
     <row r="191" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="25" t="s">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="B191" s="25" t="s">
         <v>153</v>
@@ -3905,32 +3908,32 @@
         <v>165</v>
       </c>
       <c r="D191" s="26" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="25" t="s">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="B192" s="25" t="s">
         <v>153</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="D192" s="26" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="25" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B193" s="25" t="s">
         <v>153</v>
       </c>
       <c r="C193" s="25" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="D193" s="26" t="s">
         <v>8</v>
@@ -3938,13 +3941,13 @@
     </row>
     <row r="194" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="25" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B194" s="25" t="s">
         <v>153</v>
       </c>
       <c r="C194" s="25" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D194" s="26" t="s">
         <v>8</v>
@@ -3952,21 +3955,21 @@
     </row>
     <row r="195" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="25" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B195" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="C195" s="27" t="s">
-        <v>123</v>
+      <c r="C195" s="25" t="s">
+        <v>186</v>
       </c>
       <c r="D195" s="26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="25" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B196" s="25" t="s">
         <v>153</v>
@@ -3980,7 +3983,7 @@
     </row>
     <row r="197" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B197" s="25" t="s">
         <v>153</v>
@@ -3993,44 +3996,44 @@
       </c>
     </row>
     <row r="198" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
+      <c r="A198" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="B198" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C198" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D198" s="26" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="199" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="B199" s="27" t="s">
-        <v>193</v>
+      <c r="A199" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="B199" s="25" t="s">
+        <v>153</v>
       </c>
       <c r="C199" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="D199" s="28" t="s">
+      <c r="D199" s="26" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B200" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="C200" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="D200" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="A200" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
     </row>
     <row r="201" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="27" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B201" s="27" t="s">
         <v>193</v>
@@ -4043,44 +4046,44 @@
       </c>
     </row>
     <row r="202" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="2" t="s">
+      <c r="A202" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B202" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C202" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D202" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="B203" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C203" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D203" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B202" s="2"/>
-      <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
-    </row>
-    <row r="203" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="B203" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="C203" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="D203" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="B204" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="C204" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="D204" s="30" t="s">
-        <v>12</v>
-      </c>
+      <c r="B204" s="2"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
     </row>
     <row r="205" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="29" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B205" s="29" t="s">
         <v>174</v>
@@ -4094,7 +4097,7 @@
     </row>
     <row r="206" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="29" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B206" s="29" t="s">
         <v>174</v>
@@ -4108,7 +4111,7 @@
     </row>
     <row r="207" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B207" s="29" t="s">
         <v>174</v>
@@ -4122,7 +4125,7 @@
     </row>
     <row r="208" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B208" s="29" t="s">
         <v>174</v>
@@ -4136,7 +4139,7 @@
     </row>
     <row r="209" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="29" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B209" s="29" t="s">
         <v>174</v>
@@ -4150,7 +4153,7 @@
     </row>
     <row r="210" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="29" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="B210" s="29" t="s">
         <v>174</v>
@@ -4164,7 +4167,7 @@
     </row>
     <row r="211" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B211" s="29" t="s">
         <v>174</v>
@@ -4178,7 +4181,7 @@
     </row>
     <row r="212" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="29" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="B212" s="29" t="s">
         <v>174</v>
@@ -4191,44 +4194,44 @@
       </c>
     </row>
     <row r="213" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="2" t="s">
+      <c r="A213" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="B213" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C213" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D213" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="B214" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C214" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D214" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B213" s="2"/>
-      <c r="C213" s="2"/>
-      <c r="D213" s="2"/>
-    </row>
-    <row r="214" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="B214" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="C214" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="D214" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="B215" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="C215" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="D215" s="32" t="s">
-        <v>12</v>
-      </c>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
     </row>
     <row r="216" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="31" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B216" s="31" t="s">
         <v>206</v>
@@ -4242,7 +4245,7 @@
     </row>
     <row r="217" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="31" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B217" s="31" t="s">
         <v>206</v>
@@ -4256,7 +4259,7 @@
     </row>
     <row r="218" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B218" s="31" t="s">
         <v>206</v>
@@ -4270,7 +4273,7 @@
     </row>
     <row r="219" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="31" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B219" s="31" t="s">
         <v>206</v>
@@ -4284,7 +4287,7 @@
     </row>
     <row r="220" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="31" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B220" s="31" t="s">
         <v>206</v>
@@ -4298,7 +4301,7 @@
     </row>
     <row r="221" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="31" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B221" s="31" t="s">
         <v>206</v>
@@ -4312,7 +4315,7 @@
     </row>
     <row r="222" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="31" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B222" s="31" t="s">
         <v>206</v>
@@ -4326,7 +4329,7 @@
     </row>
     <row r="223" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="31" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B223" s="31" t="s">
         <v>206</v>
@@ -4338,23 +4341,49 @@
         <v>12</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="B224" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C224" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D224" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="B225" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C225" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D225" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="241" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="242" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="243" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5103,6 +5132,8 @@
     <row r="986" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="987" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="988" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
